--- a/data/cyano_atx_24.xlsx
+++ b/data/cyano_atx_24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jld/Documents/Github/River_HAB_Modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBC280D-5AE9-C04D-A280-1FA7BB8808D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516D896E-94C5-6040-90A9-0D5214DC8149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="217">
   <si>
     <t>ESF</t>
   </si>
@@ -552,9 +552,6 @@
   </si>
   <si>
     <t>Blackwood Upper -R3</t>
-  </si>
-  <si>
-    <t>Eel-2Up</t>
   </si>
   <si>
     <t xml:space="preserve">BLANK 4 </t>
@@ -754,17 +751,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U122"/>
+  <dimension ref="A1:U120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="21" max="21" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -1123,7 +1119,6 @@
       </c>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
-      <c r="T1" s="4"/>
       <c r="U1" s="3"/>
     </row>
     <row r="2" spans="1:21" ht="22" x14ac:dyDescent="0.3">
@@ -1134,48 +1129,45 @@
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F2" s="2">
         <v>0.113</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H2">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J2">
         <v>0.05</v>
       </c>
       <c r="K2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O2" t="s">
-        <v>211</v>
-      </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="5"/>
+        <v>210</v>
+      </c>
+      <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1185,48 +1177,44 @@
         <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>0.11899999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H3">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J3">
         <v>0.05</v>
       </c>
       <c r="K3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O3" t="s">
-        <v>211</v>
-      </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1236,48 +1224,44 @@
         <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>0.108</v>
       </c>
       <c r="G4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H4">
         <v>0.09</v>
       </c>
       <c r="I4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J4">
         <v>0.05</v>
       </c>
       <c r="K4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O4" t="s">
-        <v>211</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1287,48 +1271,44 @@
         <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>0.128</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H5">
         <v>0.106</v>
       </c>
       <c r="I5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J5">
         <v>0.06</v>
       </c>
       <c r="K5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O5" t="s">
-        <v>211</v>
-      </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1338,48 +1318,44 @@
         <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F6">
         <v>0.11899999999999999</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H6">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J6">
         <v>0.05</v>
       </c>
       <c r="K6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O6" t="s">
-        <v>211</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1389,10 +1365,10 @@
         <v>139</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E7">
         <v>9.4E-2</v>
@@ -1401,36 +1377,32 @@
         <v>0.114</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H7">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J7">
         <v>0.05</v>
       </c>
       <c r="K7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L7">
         <v>9.4E-2</v>
       </c>
       <c r="M7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O7">
         <v>9.4E-2</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1440,48 +1412,44 @@
         <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>0.15</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H8">
         <v>0.124</v>
       </c>
       <c r="I8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J8">
         <v>0.06</v>
       </c>
       <c r="K8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O8" t="s">
-        <v>211</v>
-      </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1491,10 +1459,10 @@
         <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E9">
         <v>0.14399999999999999</v>
@@ -1503,36 +1471,32 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H9">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J9">
         <v>0.05</v>
       </c>
       <c r="K9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L9">
         <v>0.14399999999999999</v>
       </c>
       <c r="M9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O9">
         <v>0.14399999999999999</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1542,10 +1506,10 @@
         <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E10">
         <v>0.624</v>
@@ -1554,36 +1518,32 @@
         <v>0.115</v>
       </c>
       <c r="G10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H10">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J10">
         <v>0.05</v>
       </c>
       <c r="K10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L10">
         <v>0.624</v>
       </c>
       <c r="M10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O10">
         <v>0.624</v>
       </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1593,48 +1553,44 @@
         <v>143</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F11">
         <v>0.158</v>
       </c>
       <c r="G11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H11">
         <v>0.13100000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O11" t="s">
-        <v>211</v>
-      </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -1644,48 +1600,44 @@
         <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>0.115</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H12">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J12">
         <v>0.05</v>
       </c>
       <c r="K12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O12" t="s">
-        <v>211</v>
-      </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1695,48 +1647,44 @@
         <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F13">
         <v>0.111</v>
       </c>
       <c r="G13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H13">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J13">
         <v>0.05</v>
       </c>
       <c r="K13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O13" t="s">
-        <v>211</v>
-      </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1746,48 +1694,44 @@
         <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F14">
         <v>0.109</v>
       </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H14">
         <v>0.09</v>
       </c>
       <c r="I14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J14">
         <v>0.05</v>
       </c>
       <c r="K14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O14" t="s">
-        <v>211</v>
-      </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1797,10 +1741,10 @@
         <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E15">
         <v>0.47</v>
@@ -1809,19 +1753,19 @@
         <v>0.112</v>
       </c>
       <c r="G15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H15">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J15">
         <v>0.05</v>
       </c>
       <c r="K15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L15">
         <v>0.11899999999999999</v>
@@ -1835,10 +1779,6 @@
       <c r="O15">
         <v>0.47</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1848,50 +1788,46 @@
         <v>148</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F16">
         <v>0.111</v>
       </c>
       <c r="G16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H16">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J16">
         <v>0.05</v>
       </c>
       <c r="K16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O16" t="s">
-        <v>211</v>
-      </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1899,50 +1835,46 @@
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F17">
         <v>0.121</v>
       </c>
       <c r="G17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H17">
         <v>0.1</v>
       </c>
       <c r="I17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J17">
         <v>0.05</v>
       </c>
       <c r="K17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s">
-        <v>211</v>
-      </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1950,50 +1882,46 @@
         <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F18">
         <v>0.11899999999999999</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H18">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J18">
         <v>0.05</v>
       </c>
       <c r="K18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s">
-        <v>211</v>
-      </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -2001,10 +1929,10 @@
         <v>149</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E19">
         <v>2.1999999999999999E-2</v>
@@ -2013,38 +1941,34 @@
         <v>0.121</v>
       </c>
       <c r="G19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H19">
         <v>0.10100000000000001</v>
       </c>
       <c r="I19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J19">
         <v>0.05</v>
       </c>
       <c r="K19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L19">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O19">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -2052,50 +1976,46 @@
         <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F20">
         <v>0.121</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H20">
         <v>0.10100000000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J20">
         <v>0.05</v>
       </c>
       <c r="K20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O20" t="s">
-        <v>211</v>
-      </c>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -2103,10 +2023,10 @@
         <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E21">
         <v>9.8000000000000004E-2</v>
@@ -2115,38 +2035,34 @@
         <v>0.155</v>
       </c>
       <c r="G21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H21">
         <v>0.128</v>
       </c>
       <c r="I21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J21">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L21">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="M21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O21">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2154,50 +2070,46 @@
         <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F22">
         <v>0.14699999999999999</v>
       </c>
       <c r="G22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H22">
         <v>0.122</v>
       </c>
       <c r="I22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J22">
         <v>0.06</v>
       </c>
       <c r="K22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O22" t="s">
-        <v>211</v>
-      </c>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -2205,10 +2117,10 @@
         <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E23">
         <v>5.0999999999999997E-2</v>
@@ -2217,38 +2129,34 @@
         <v>0.109</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H23">
         <v>0.09</v>
       </c>
       <c r="I23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J23">
         <v>0.05</v>
       </c>
       <c r="K23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L23">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="M23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O23">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -2256,10 +2164,10 @@
         <v>151</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E24">
         <v>6.4000000000000001E-2</v>
@@ -2268,38 +2176,34 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H24">
         <v>0.111</v>
       </c>
       <c r="I24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J24">
         <v>0.06</v>
       </c>
       <c r="K24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L24">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="M24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O24">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -2307,10 +2211,10 @@
         <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E25">
         <v>0.10199999999999999</v>
@@ -2319,38 +2223,34 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="G25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H25">
         <v>0.109</v>
       </c>
       <c r="I25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J25">
         <v>0.06</v>
       </c>
       <c r="K25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L25">
         <v>0.10199999999999999</v>
       </c>
       <c r="M25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O25">
         <v>0.10199999999999999</v>
       </c>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -2358,50 +2258,46 @@
         <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26">
         <v>3.39</v>
       </c>
       <c r="G26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H26">
         <v>1.9370000000000001</v>
       </c>
       <c r="I26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J26">
         <v>1.01</v>
       </c>
       <c r="K26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O26" t="s">
-        <v>211</v>
-      </c>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2409,10 +2305,10 @@
         <v>154</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E27">
         <v>9.6000000000000002E-2</v>
@@ -2421,38 +2317,34 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H27">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J27">
         <v>0.05</v>
       </c>
       <c r="K27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L27">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="M27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O27">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -2460,10 +2352,10 @@
         <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E28">
         <v>0.158</v>
@@ -2472,38 +2364,34 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="G28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H28">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J28">
         <v>0.05</v>
       </c>
       <c r="K28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L28">
         <v>0.158</v>
       </c>
       <c r="M28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O28">
         <v>0.158</v>
       </c>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2511,10 +2399,10 @@
         <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E29">
         <v>8.5999999999999993E-2</v>
@@ -2523,38 +2411,34 @@
         <v>0.21</v>
       </c>
       <c r="G29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H29">
         <v>0.12</v>
       </c>
       <c r="I29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J29">
         <v>0.06</v>
       </c>
       <c r="K29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L29">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="M29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O29">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2562,10 +2446,10 @@
         <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E30">
         <v>6.6000000000000003E-2</v>
@@ -2574,38 +2458,34 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H30">
         <v>0.10100000000000001</v>
       </c>
       <c r="I30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J30">
         <v>0.05</v>
       </c>
       <c r="K30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L30">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="M30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O30">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -2613,10 +2493,10 @@
         <v>149</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E31">
         <v>2.5310000000000001</v>
@@ -2625,13 +2505,13 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H31">
         <v>0.13100000000000001</v>
       </c>
       <c r="I31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J31">
         <v>7.0000000000000007E-2</v>
@@ -2643,20 +2523,16 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="M31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O31">
         <v>2.5310000000000001</v>
       </c>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -2664,10 +2540,10 @@
         <v>149</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E32">
         <v>0.47499999999999998</v>
@@ -2676,13 +2552,13 @@
         <v>0.159</v>
       </c>
       <c r="G32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H32">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J32">
         <v>0.05</v>
@@ -2694,20 +2570,16 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="M32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O32">
         <v>0.47499999999999998</v>
       </c>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2715,10 +2587,10 @@
         <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E33">
         <v>0.47099999999999997</v>
@@ -2727,13 +2599,13 @@
         <v>0.214</v>
       </c>
       <c r="G33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H33">
         <v>0.122</v>
       </c>
       <c r="I33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J33">
         <v>0.06</v>
@@ -2745,20 +2617,16 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="M33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O33">
         <v>0.47099999999999997</v>
       </c>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2766,10 +2634,10 @@
         <v>157</v>
       </c>
       <c r="C34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E34">
         <v>0.66800000000000004</v>
@@ -2778,13 +2646,13 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="G34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H34">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J34">
         <v>0.05</v>
@@ -2796,20 +2664,16 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="M34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O34">
         <v>0.66800000000000004</v>
       </c>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2817,10 +2681,10 @@
         <v>149</v>
       </c>
       <c r="C35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E35">
         <v>2.4969999999999999</v>
@@ -2829,13 +2693,13 @@
         <v>0.17</v>
       </c>
       <c r="G35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H35">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J35">
         <v>0.05</v>
@@ -2847,20 +2711,16 @@
         <v>0.59599999999999997</v>
       </c>
       <c r="M35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O35">
         <v>2.4969999999999999</v>
       </c>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2868,10 +2728,10 @@
         <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E36">
         <v>0.59399999999999997</v>
@@ -2880,13 +2740,13 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="G36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H36">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J36">
         <v>0.05</v>
@@ -2895,23 +2755,19 @@
         <v>0.59399999999999997</v>
       </c>
       <c r="L36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O36">
         <v>0.59399999999999997</v>
       </c>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2919,10 +2775,10 @@
         <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37">
         <v>0.29799999999999999</v>
@@ -2931,13 +2787,13 @@
         <v>0.19900000000000001</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H37">
         <v>0.114</v>
       </c>
       <c r="I37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J37">
         <v>0.06</v>
@@ -2946,23 +2802,19 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="L37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M37">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="N37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O37" t="s">
-        <v>211</v>
-      </c>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2970,10 +2822,10 @@
         <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E38">
         <v>8.1000000000000003E-2</v>
@@ -2982,38 +2834,34 @@
         <v>0.16900000000000001</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H38">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J38">
         <v>0.05</v>
       </c>
       <c r="K38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L38">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="M38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O38">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3021,50 +2869,46 @@
         <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F39">
         <v>0.30099999999999999</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H39">
         <v>0.17199999999999999</v>
       </c>
       <c r="I39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J39">
         <v>0.09</v>
       </c>
       <c r="K39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O39" t="s">
-        <v>211</v>
-      </c>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -3072,10 +2916,10 @@
         <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E40">
         <v>0.88</v>
@@ -3084,13 +2928,13 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="G40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H40">
         <v>0.10299999999999999</v>
       </c>
       <c r="I40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J40">
         <v>0.05</v>
@@ -3102,20 +2946,16 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="M40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O40">
         <v>0.88</v>
       </c>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -3123,10 +2963,10 @@
         <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E41">
         <v>1.988</v>
@@ -3135,13 +2975,13 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H41">
         <v>0.1</v>
       </c>
       <c r="I41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J41">
         <v>0.05</v>
@@ -3153,20 +2993,16 @@
         <v>0.77</v>
       </c>
       <c r="M41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O41">
         <v>1.988</v>
       </c>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -3174,10 +3010,10 @@
         <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E42">
         <v>0.76</v>
@@ -3186,13 +3022,13 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H42">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J42">
         <v>0.05</v>
@@ -3204,20 +3040,16 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="M42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O42">
         <v>0.76</v>
       </c>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3225,10 +3057,10 @@
         <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E43">
         <v>0.64300000000000002</v>
@@ -3237,13 +3069,13 @@
         <v>0.18</v>
       </c>
       <c r="G43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H43">
         <v>0.10299999999999999</v>
       </c>
       <c r="I43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J43">
         <v>0.05</v>
@@ -3255,20 +3087,16 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="M43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O43" t="s">
-        <v>211</v>
-      </c>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -3276,10 +3104,10 @@
         <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E44">
         <v>6.0549999999999997</v>
@@ -3288,13 +3116,13 @@
         <v>0.17</v>
       </c>
       <c r="G44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H44">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J44">
         <v>0.05</v>
@@ -3306,20 +3134,16 @@
         <v>0.63500000000000001</v>
       </c>
       <c r="M44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O44">
         <v>6.0549999999999997</v>
       </c>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -3327,10 +3151,10 @@
         <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E45">
         <v>5.2670000000000003</v>
@@ -3339,38 +3163,34 @@
         <v>0.183</v>
       </c>
       <c r="G45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H45">
         <v>0.105</v>
       </c>
       <c r="I45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J45">
         <v>0.05</v>
       </c>
       <c r="K45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O45" t="s">
-        <v>211</v>
-      </c>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -3378,50 +3198,46 @@
         <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F46">
         <v>3.39</v>
       </c>
       <c r="G46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H46">
         <v>1.9370000000000001</v>
       </c>
       <c r="I46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J46">
         <v>1.01</v>
       </c>
       <c r="K46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O46" t="s">
-        <v>211</v>
-      </c>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -3429,10 +3245,10 @@
         <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E47">
         <v>0.36299999999999999</v>
@@ -3441,13 +3257,13 @@
         <v>0.16</v>
       </c>
       <c r="G47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H47">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J47">
         <v>0.05</v>
@@ -3456,23 +3272,19 @@
         <v>0.36299999999999999</v>
       </c>
       <c r="L47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O47" t="s">
-        <v>211</v>
-      </c>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3480,10 +3292,10 @@
         <v>150</v>
       </c>
       <c r="C48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E48">
         <v>4.8780000000000001</v>
@@ -3492,13 +3304,13 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="G48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H48">
         <v>9.4E-2</v>
       </c>
       <c r="I48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J48">
         <v>0.05</v>
@@ -3510,20 +3322,16 @@
         <v>1.389</v>
       </c>
       <c r="M48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O48">
         <v>4.8780000000000001</v>
       </c>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -3531,10 +3339,10 @@
         <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E49">
         <v>5.8999999999999997E-2</v>
@@ -3543,38 +3351,34 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="G49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H49">
         <v>0.10199999999999999</v>
       </c>
       <c r="I49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J49">
         <v>0.05</v>
       </c>
       <c r="K49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L49">
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="M49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O49">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3582,10 +3386,10 @@
         <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E50">
         <v>1.2410000000000001</v>
@@ -3594,13 +3398,13 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="G50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H50">
         <v>0.121</v>
       </c>
       <c r="I50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J50">
         <v>0.06</v>
@@ -3612,20 +3416,16 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="M50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O50">
         <v>1.2410000000000001</v>
       </c>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -3633,50 +3433,46 @@
         <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F51">
         <v>0.16600000000000001</v>
       </c>
       <c r="G51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H51">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J51">
         <v>0.05</v>
       </c>
       <c r="K51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O51" t="s">
-        <v>211</v>
-      </c>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -3684,50 +3480,46 @@
         <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F52">
         <v>0.18</v>
       </c>
       <c r="G52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H52">
         <v>0.10299999999999999</v>
       </c>
       <c r="I52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J52">
         <v>0.05</v>
       </c>
       <c r="K52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O52" t="s">
-        <v>211</v>
-      </c>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -3735,50 +3527,46 @@
         <v>161</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F53">
         <v>0.161</v>
       </c>
       <c r="G53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H53">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J53">
         <v>0.05</v>
       </c>
       <c r="K53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O53" t="s">
-        <v>211</v>
-      </c>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -3786,10 +3574,10 @@
         <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E54">
         <v>0.97699999999999998</v>
@@ -3798,13 +3586,13 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="G54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H54">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J54">
         <v>0.05</v>
@@ -3816,20 +3604,16 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="M54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O54">
         <v>0.97699999999999998</v>
       </c>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -3837,10 +3621,10 @@
         <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E55">
         <v>1.2010000000000001</v>
@@ -3849,13 +3633,13 @@
         <v>0.187</v>
       </c>
       <c r="G55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H55">
         <v>0.107</v>
       </c>
       <c r="I55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J55">
         <v>0.06</v>
@@ -3867,20 +3651,16 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="M55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O55">
         <v>1.2010000000000001</v>
       </c>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3888,10 +3668,10 @@
         <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E56">
         <v>1.1559999999999999</v>
@@ -3900,13 +3680,13 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="G56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H56">
         <v>0.111</v>
       </c>
       <c r="I56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J56">
         <v>0.06</v>
@@ -3918,20 +3698,16 @@
         <v>0.22</v>
       </c>
       <c r="M56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O56">
         <v>1.1559999999999999</v>
       </c>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -3939,50 +3715,46 @@
         <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F57">
         <v>0.16</v>
       </c>
       <c r="G57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H57">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J57">
         <v>0.05</v>
       </c>
       <c r="K57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O57" t="s">
-        <v>211</v>
-      </c>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -3990,50 +3762,46 @@
         <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F58">
         <v>0.17699999999999999</v>
       </c>
       <c r="G58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H58">
         <v>0.10100000000000001</v>
       </c>
       <c r="I58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J58">
         <v>0.05</v>
       </c>
       <c r="K58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N58" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O58" t="s">
-        <v>211</v>
-      </c>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -4041,50 +3809,46 @@
         <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59">
         <v>0.16400000000000001</v>
       </c>
       <c r="G59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H59">
         <v>9.4E-2</v>
       </c>
       <c r="I59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J59">
         <v>0.05</v>
       </c>
       <c r="K59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O59" t="s">
-        <v>211</v>
-      </c>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -4092,50 +3856,46 @@
         <v>162</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F60">
         <v>0.17799999999999999</v>
       </c>
       <c r="G60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H60">
         <v>0.10199999999999999</v>
       </c>
       <c r="I60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J60">
         <v>0.05</v>
       </c>
       <c r="K60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O60" t="s">
-        <v>211</v>
-      </c>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -4143,50 +3903,46 @@
         <v>145</v>
       </c>
       <c r="C61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F61">
         <v>0.17699999999999999</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H61">
         <v>0.10100000000000001</v>
       </c>
       <c r="I61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J61">
         <v>0.05</v>
       </c>
       <c r="K61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O61" t="s">
-        <v>211</v>
-      </c>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -4194,50 +3950,46 @@
         <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F62">
         <v>0.17100000000000001</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H62">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J62">
         <v>0.05</v>
       </c>
       <c r="K62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O62" t="s">
-        <v>211</v>
-      </c>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -4245,50 +3997,46 @@
         <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F63">
         <v>0.17100000000000001</v>
       </c>
       <c r="G63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H63">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J63">
         <v>0.05</v>
       </c>
       <c r="K63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O63" t="s">
-        <v>211</v>
-      </c>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -4296,50 +4044,46 @@
         <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F64">
         <v>0.161</v>
       </c>
       <c r="G64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H64">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J64">
         <v>0.05</v>
       </c>
       <c r="K64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O64" t="s">
-        <v>211</v>
-      </c>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>78</v>
       </c>
@@ -4347,50 +4091,46 @@
         <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F65">
         <v>0.17699999999999999</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H65">
         <v>0.10100000000000001</v>
       </c>
       <c r="I65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J65">
         <v>0.05</v>
       </c>
       <c r="K65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O65" t="s">
-        <v>211</v>
-      </c>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>79</v>
       </c>
@@ -4398,50 +4138,46 @@
         <v>140</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D66" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F66">
         <v>1.335</v>
       </c>
       <c r="G66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H66">
         <v>0.76200000000000001</v>
       </c>
       <c r="I66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J66">
         <v>0.4</v>
       </c>
       <c r="K66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O66" t="s">
-        <v>211</v>
-      </c>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -4449,50 +4185,46 @@
         <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D67" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F67">
         <v>0.17899999999999999</v>
       </c>
       <c r="G67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H67">
         <v>0.10199999999999999</v>
       </c>
       <c r="I67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J67">
         <v>0.05</v>
       </c>
       <c r="K67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O67" t="s">
-        <v>211</v>
-      </c>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -4500,50 +4232,46 @@
         <v>144</v>
       </c>
       <c r="C68" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F68">
         <v>0.159</v>
       </c>
       <c r="G68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H68">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J68">
         <v>0.05</v>
       </c>
       <c r="K68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N68" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O68" t="s">
-        <v>211</v>
-      </c>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>82</v>
       </c>
@@ -4551,50 +4279,46 @@
         <v>147</v>
       </c>
       <c r="C69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F69">
         <v>0.33400000000000002</v>
       </c>
       <c r="G69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H69">
         <v>0.191</v>
       </c>
       <c r="I69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J69">
         <v>0.1</v>
       </c>
       <c r="K69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O69" t="s">
-        <v>211</v>
-      </c>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -4602,50 +4326,46 @@
         <v>145</v>
       </c>
       <c r="C70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F70">
         <v>0.16800000000000001</v>
       </c>
       <c r="G70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H70">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="I70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J70">
         <v>0.05</v>
       </c>
       <c r="K70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N70" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O70" t="s">
-        <v>211</v>
-      </c>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -4653,50 +4373,46 @@
         <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D71" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F71">
         <v>3.39</v>
       </c>
       <c r="G71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H71">
         <v>1.9370000000000001</v>
       </c>
       <c r="I71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J71">
         <v>1.01</v>
       </c>
       <c r="K71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O71" t="s">
-        <v>211</v>
-      </c>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -4704,10 +4420,10 @@
         <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D72" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E72">
         <v>2.0510000000000002</v>
@@ -4716,13 +4432,13 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="G72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H72">
         <v>0.10199999999999999</v>
       </c>
       <c r="I72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J72">
         <v>0.05</v>
@@ -4734,20 +4450,16 @@
         <v>0.61599999999999999</v>
       </c>
       <c r="M72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O72">
         <v>2.0510000000000002</v>
       </c>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>86</v>
       </c>
@@ -4755,10 +4467,10 @@
         <v>149</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E73">
         <v>2.0830000000000002</v>
@@ -4767,13 +4479,13 @@
         <v>0.17</v>
       </c>
       <c r="G73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H73">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J73">
         <v>0.05</v>
@@ -4785,20 +4497,16 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="M73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O73">
         <v>2.0830000000000002</v>
       </c>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4806,10 +4514,10 @@
         <v>150</v>
       </c>
       <c r="C74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E74">
         <v>0.34100000000000003</v>
@@ -4818,13 +4526,13 @@
         <v>0.159</v>
       </c>
       <c r="G74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H74">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J74">
         <v>0.05</v>
@@ -4836,20 +4544,16 @@
         <v>7.8E-2</v>
       </c>
       <c r="M74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O74">
         <v>0.34100000000000003</v>
       </c>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -4857,10 +4561,10 @@
         <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D75" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E75">
         <v>2.242</v>
@@ -4869,13 +4573,13 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="G75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H75">
         <v>0.11899999999999999</v>
       </c>
       <c r="I75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J75">
         <v>0.06</v>
@@ -4887,20 +4591,16 @@
         <v>0.81799999999999995</v>
       </c>
       <c r="M75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O75">
         <v>2.242</v>
       </c>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>89</v>
       </c>
@@ -4908,10 +4608,10 @@
         <v>154</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D76" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E76">
         <v>1.6970000000000001</v>
@@ -4920,13 +4620,13 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="G76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H76">
         <v>0.10199999999999999</v>
       </c>
       <c r="I76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J76">
         <v>0.05</v>
@@ -4938,20 +4638,16 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="M76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O76">
         <v>1.6970000000000001</v>
       </c>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>90</v>
       </c>
@@ -4959,10 +4655,10 @@
         <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E77">
         <v>6.7</v>
@@ -4971,13 +4667,13 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="G77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H77">
         <v>0.11899999999999999</v>
       </c>
       <c r="I77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J77">
         <v>0.06</v>
@@ -4989,20 +4685,16 @@
         <v>1.744</v>
       </c>
       <c r="M77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O77">
         <v>6.7</v>
       </c>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -5010,10 +4702,10 @@
         <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E78">
         <v>6.4569999999999999</v>
@@ -5022,13 +4714,13 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="G78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H78">
         <v>0.10100000000000001</v>
       </c>
       <c r="I78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J78">
         <v>0.05</v>
@@ -5040,20 +4732,16 @@
         <v>1.768</v>
       </c>
       <c r="M78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O78">
         <v>6.4569999999999999</v>
       </c>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>92</v>
       </c>
@@ -5061,10 +4749,10 @@
         <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E79">
         <v>6.577</v>
@@ -5073,13 +4761,13 @@
         <v>0.19</v>
       </c>
       <c r="G79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H79">
         <v>0.109</v>
       </c>
       <c r="I79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J79">
         <v>0.06</v>
@@ -5091,20 +4779,16 @@
         <v>2.0259999999999998</v>
       </c>
       <c r="M79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O79">
         <v>6.577</v>
       </c>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>93</v>
       </c>
@@ -5112,10 +4796,10 @@
         <v>155</v>
       </c>
       <c r="C80" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D80" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E80">
         <v>1.0669999999999999</v>
@@ -5124,13 +4808,13 @@
         <v>0.182</v>
       </c>
       <c r="G80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H80">
         <v>0.104</v>
       </c>
       <c r="I80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J80">
         <v>0.05</v>
@@ -5142,20 +4826,16 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="M80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O80">
         <v>1.0669999999999999</v>
       </c>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -5163,10 +4843,10 @@
         <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D81" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E81">
         <v>1.1719999999999999</v>
@@ -5175,13 +4855,13 @@
         <v>0.17</v>
       </c>
       <c r="G81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H81">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="I81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J81">
         <v>0.05</v>
@@ -5193,20 +4873,16 @@
         <v>0.42599999999999999</v>
       </c>
       <c r="M81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O81">
         <v>1.1719999999999999</v>
       </c>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="4"/>
-      <c r="U81" s="4"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -5214,50 +4890,46 @@
         <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F82">
         <v>0.17299999999999999</v>
       </c>
       <c r="G82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H82">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J82">
         <v>0.05</v>
       </c>
       <c r="K82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O82" t="s">
-        <v>211</v>
-      </c>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>96</v>
       </c>
@@ -5265,50 +4937,46 @@
         <v>138</v>
       </c>
       <c r="C83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D83" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83">
         <v>0.17699999999999999</v>
       </c>
       <c r="G83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H83">
         <v>0.10100000000000001</v>
       </c>
       <c r="I83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J83">
         <v>0.05</v>
       </c>
       <c r="K83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O83" t="s">
-        <v>211</v>
-      </c>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -5316,50 +4984,46 @@
         <v>136</v>
       </c>
       <c r="C84" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D84" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F84">
         <v>0.16</v>
       </c>
       <c r="G84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H84">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J84">
         <v>0.05</v>
       </c>
       <c r="K84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O84" t="s">
-        <v>211</v>
-      </c>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -5367,50 +5031,46 @@
         <v>143</v>
       </c>
       <c r="C85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D85" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F85">
         <v>0.17399999999999999</v>
       </c>
       <c r="G85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H85">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J85">
         <v>0.05</v>
       </c>
       <c r="K85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O85" t="s">
-        <v>211</v>
-      </c>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -5418,50 +5078,46 @@
         <v>145</v>
       </c>
       <c r="C86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F86">
         <v>0.16600000000000001</v>
       </c>
       <c r="G86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H86">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J86">
         <v>0.05</v>
       </c>
       <c r="K86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N86" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O86" t="s">
-        <v>211</v>
-      </c>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>100</v>
       </c>
@@ -5469,50 +5125,46 @@
         <v>148</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D87" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F87">
         <v>0.17799999999999999</v>
       </c>
       <c r="G87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H87">
         <v>0.10199999999999999</v>
       </c>
       <c r="I87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J87">
         <v>0.05</v>
       </c>
       <c r="K87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O87" t="s">
-        <v>211</v>
-      </c>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -5520,10 +5172,10 @@
         <v>141</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D88" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E88">
         <v>0.55700000000000005</v>
@@ -5532,38 +5184,34 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H88">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J88">
         <v>0.05</v>
       </c>
       <c r="K88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L88">
         <v>0.55700000000000005</v>
       </c>
       <c r="M88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O88">
         <v>0.55700000000000005</v>
       </c>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>102</v>
       </c>
@@ -5571,50 +5219,46 @@
         <v>149</v>
       </c>
       <c r="C89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D89" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F89">
         <v>0.24199999999999999</v>
       </c>
       <c r="G89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H89">
         <v>0.13800000000000001</v>
       </c>
       <c r="I89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J89">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O89" t="s">
-        <v>211</v>
-      </c>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>103</v>
       </c>
@@ -5622,50 +5266,46 @@
         <v>150</v>
       </c>
       <c r="C90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D90" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F90">
         <v>0.16600000000000001</v>
       </c>
       <c r="G90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H90">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J90">
         <v>0.05</v>
       </c>
       <c r="K90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N90" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O90" t="s">
-        <v>211</v>
-      </c>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -5673,50 +5313,46 @@
         <v>151</v>
       </c>
       <c r="C91" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D91" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F91">
         <v>0.16200000000000001</v>
       </c>
       <c r="G91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H91">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J91">
         <v>0.05</v>
       </c>
       <c r="K91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N91" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O91" t="s">
-        <v>211</v>
-      </c>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -5724,50 +5360,46 @@
         <v>169</v>
       </c>
       <c r="C92" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F92">
         <v>0.17199999999999999</v>
       </c>
       <c r="G92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H92">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J92">
         <v>0.05</v>
       </c>
       <c r="K92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O92" t="s">
-        <v>211</v>
-      </c>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>106</v>
       </c>
@@ -5775,50 +5407,46 @@
         <v>154</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F93">
         <v>0.18099999999999999</v>
       </c>
       <c r="G93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H93">
         <v>0.10299999999999999</v>
       </c>
       <c r="I93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J93">
         <v>0.05</v>
       </c>
       <c r="K93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O93" t="s">
-        <v>211</v>
-      </c>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>107</v>
       </c>
@@ -5826,50 +5454,46 @@
         <v>155</v>
       </c>
       <c r="C94" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D94" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F94">
         <v>0.17499999999999999</v>
       </c>
       <c r="G94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H94">
         <v>0.1</v>
       </c>
       <c r="I94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J94">
         <v>0.05</v>
       </c>
       <c r="K94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O94" t="s">
-        <v>211</v>
-      </c>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -5877,50 +5501,46 @@
         <v>149</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F95">
         <v>0.17299999999999999</v>
       </c>
       <c r="G95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H95">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J95">
         <v>0.05</v>
       </c>
       <c r="K95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O95" t="s">
-        <v>211</v>
-      </c>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>109</v>
       </c>
@@ -5928,10 +5548,10 @@
         <v>156</v>
       </c>
       <c r="C96" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E96">
         <v>7.0999999999999994E-2</v>
@@ -5940,38 +5560,34 @@
         <v>0.18</v>
       </c>
       <c r="G96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H96">
         <v>0.10299999999999999</v>
       </c>
       <c r="I96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J96">
         <v>0.05</v>
       </c>
       <c r="K96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L96">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="M96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O96">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>110</v>
       </c>
@@ -5979,10 +5595,10 @@
         <v>157</v>
       </c>
       <c r="C97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E97">
         <v>8.7999999999999995E-2</v>
@@ -5991,38 +5607,34 @@
         <v>0.157</v>
       </c>
       <c r="G97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H97">
         <v>0.09</v>
       </c>
       <c r="I97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J97">
         <v>0.05</v>
       </c>
       <c r="K97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L97">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="M97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O97" t="s">
-        <v>211</v>
-      </c>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -6030,50 +5642,46 @@
         <v>150</v>
       </c>
       <c r="C98" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F98">
         <v>0.183</v>
       </c>
       <c r="G98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H98">
         <v>0.104</v>
       </c>
       <c r="I98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J98">
         <v>0.05</v>
       </c>
       <c r="K98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O98" t="s">
-        <v>211</v>
-      </c>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>112</v>
       </c>
@@ -6081,50 +5689,46 @@
         <v>154</v>
       </c>
       <c r="C99" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D99" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F99">
         <v>0.18</v>
       </c>
       <c r="G99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H99">
         <v>0.10299999999999999</v>
       </c>
       <c r="I99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J99">
         <v>0.05</v>
       </c>
       <c r="K99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O99" t="s">
-        <v>211</v>
-      </c>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>113</v>
       </c>
@@ -6132,50 +5736,46 @@
         <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100">
         <v>0.159</v>
       </c>
       <c r="G100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H100">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="I100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J100">
         <v>0.05</v>
       </c>
       <c r="K100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O100" t="s">
-        <v>211</v>
-      </c>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -6183,50 +5783,46 @@
         <v>149</v>
       </c>
       <c r="C101" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D101" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101">
         <v>0.17499999999999999</v>
       </c>
       <c r="G101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H101">
         <v>0.1</v>
       </c>
       <c r="I101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J101">
         <v>0.05</v>
       </c>
       <c r="K101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O101" t="s">
-        <v>211</v>
-      </c>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -6234,50 +5830,46 @@
         <v>146</v>
       </c>
       <c r="C102" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D102" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F102">
         <v>0.29899999999999999</v>
       </c>
       <c r="G102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H102">
         <v>0.17100000000000001</v>
       </c>
       <c r="I102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J102">
         <v>0.09</v>
       </c>
       <c r="K102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O102" t="s">
-        <v>211</v>
-      </c>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -6285,10 +5877,10 @@
         <v>148</v>
       </c>
       <c r="C103" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D103" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E103">
         <v>12.085000000000001</v>
@@ -6297,13 +5889,13 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H103">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="I103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J103">
         <v>0.05</v>
@@ -6323,12 +5915,8 @@
       <c r="O103">
         <v>12.085000000000001</v>
       </c>
-      <c r="R103" s="4"/>
-      <c r="S103" s="4"/>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -6336,10 +5924,10 @@
         <v>141</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D104" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E104">
         <v>0.59199999999999997</v>
@@ -6348,38 +5936,34 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="G104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H104">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J104">
         <v>0.05</v>
       </c>
       <c r="K104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L104">
         <v>0.59199999999999997</v>
       </c>
       <c r="M104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O104">
         <v>0.59199999999999997</v>
       </c>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -6387,50 +5971,46 @@
         <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D105" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F105">
         <v>0.28299999999999997</v>
       </c>
       <c r="G105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H105">
         <v>0.16200000000000001</v>
       </c>
       <c r="I105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J105">
         <v>0.08</v>
       </c>
       <c r="K105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O105" t="s">
-        <v>211</v>
-      </c>
-      <c r="R105" s="4"/>
-      <c r="S105" s="4"/>
-      <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -6438,10 +6018,10 @@
         <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D106" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E106">
         <v>0.215</v>
@@ -6450,38 +6030,34 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="G106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H106">
         <v>0.1</v>
       </c>
       <c r="I106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J106">
         <v>0.05</v>
       </c>
       <c r="K106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L106">
         <v>0.215</v>
       </c>
       <c r="M106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N106" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O106">
         <v>0.215</v>
       </c>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -6489,50 +6065,46 @@
         <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F107">
         <v>0.17299999999999999</v>
       </c>
       <c r="G107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H107">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J107">
         <v>0.05</v>
       </c>
       <c r="K107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O107" t="s">
-        <v>211</v>
-      </c>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
-      <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -6540,50 +6112,46 @@
         <v>143</v>
       </c>
       <c r="C108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D108" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F108">
         <v>0.16300000000000001</v>
       </c>
       <c r="G108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H108">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J108">
         <v>0.05</v>
       </c>
       <c r="K108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O108" t="s">
-        <v>211</v>
-      </c>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>122</v>
       </c>
@@ -6591,50 +6159,46 @@
         <v>170</v>
       </c>
       <c r="C109" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F109">
         <v>0.16300000000000001</v>
       </c>
       <c r="G109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H109">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I109" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J109">
         <v>0.05</v>
       </c>
       <c r="K109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O109" t="s">
-        <v>211</v>
-      </c>
-      <c r="R109" s="4"/>
-      <c r="S109" s="4"/>
-      <c r="T109" s="4"/>
-      <c r="U109" s="4"/>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -6642,50 +6206,46 @@
         <v>171</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D110" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F110">
         <v>0.17199999999999999</v>
       </c>
       <c r="G110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H110">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J110">
         <v>0.05</v>
       </c>
       <c r="K110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O110" t="s">
-        <v>211</v>
-      </c>
-      <c r="R110" s="4"/>
-      <c r="S110" s="4"/>
-      <c r="T110" s="4"/>
-      <c r="U110" s="4"/>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -6693,50 +6253,46 @@
         <v>172</v>
       </c>
       <c r="C111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D111" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F111">
         <v>0.189</v>
       </c>
       <c r="G111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H111">
         <v>0.108</v>
       </c>
       <c r="I111" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J111">
         <v>0.06</v>
       </c>
       <c r="K111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N111" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O111" t="s">
-        <v>211</v>
-      </c>
-      <c r="R111" s="4"/>
-      <c r="S111" s="4"/>
-      <c r="T111" s="4"/>
-      <c r="U111" s="4"/>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -6744,50 +6300,46 @@
         <v>149</v>
       </c>
       <c r="C112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D112" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112">
         <v>0.156</v>
       </c>
       <c r="G112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H112">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="I112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J112">
         <v>0.05</v>
       </c>
       <c r="K112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N112" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O112" t="s">
-        <v>211</v>
-      </c>
-      <c r="R112" s="4"/>
-      <c r="S112" s="4"/>
-      <c r="T112" s="4"/>
-      <c r="U112" s="4"/>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -6795,232 +6347,216 @@
         <v>149</v>
       </c>
       <c r="C113" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F113">
         <v>4.5810000000000004</v>
       </c>
       <c r="G113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H113">
         <v>2.617</v>
       </c>
       <c r="I113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J113">
         <v>1.37</v>
       </c>
       <c r="K113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O113" t="s">
-        <v>211</v>
-      </c>
-      <c r="R113" s="4"/>
-      <c r="S113" s="4"/>
-      <c r="T113" s="4"/>
-      <c r="U113" s="4"/>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>127</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F114">
         <v>2.4929999999999999</v>
       </c>
       <c r="G114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H114">
         <v>1.4239999999999999</v>
       </c>
       <c r="I114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J114">
         <v>0.74</v>
       </c>
       <c r="K114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O114" t="s">
-        <v>211</v>
-      </c>
-      <c r="R114" s="4"/>
-      <c r="S114" s="4"/>
-      <c r="T114" s="4"/>
-      <c r="U114" s="4"/>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>128</v>
       </c>
       <c r="B115" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C115" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D115" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F115">
         <v>3.39</v>
       </c>
       <c r="G115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H115">
         <v>1.9370000000000001</v>
       </c>
       <c r="I115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J115">
         <v>1.01</v>
       </c>
       <c r="K115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O115" t="s">
-        <v>211</v>
-      </c>
-      <c r="R115" s="4"/>
-      <c r="S115" s="4"/>
-      <c r="T115" s="4"/>
-      <c r="U115" s="4"/>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>129</v>
       </c>
       <c r="B116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L116">
         <v>0.217</v>
       </c>
       <c r="M116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O116">
         <v>0.217</v>
       </c>
-      <c r="R116" s="4"/>
-      <c r="S116" s="4"/>
-      <c r="T116" s="4"/>
-      <c r="U116" s="4"/>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>130</v>
       </c>
       <c r="B117" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C117" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K117">
         <v>2.2949999999999999</v>
@@ -7029,151 +6565,139 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="M117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O117">
         <v>2.9079999999999999</v>
       </c>
-      <c r="R117" s="4"/>
-      <c r="S117" s="4"/>
-      <c r="T117" s="4"/>
-      <c r="U117" s="4"/>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C118" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K118" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L118">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="M118" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N118" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O118" t="s">
-        <v>211</v>
-      </c>
-      <c r="R118" s="4"/>
-      <c r="S118" s="4"/>
-      <c r="T118" s="4"/>
-      <c r="U118" s="4"/>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>132</v>
       </c>
       <c r="B119" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K119" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L119" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M119" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N119" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O119" t="s">
-        <v>211</v>
-      </c>
-      <c r="R119" s="4"/>
-      <c r="S119" s="4"/>
-      <c r="T119" s="4"/>
-      <c r="U119" s="4"/>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>133</v>
       </c>
       <c r="B120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C120" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K120">
         <v>1.302</v>
@@ -7182,30 +6706,14 @@
         <v>0.254</v>
       </c>
       <c r="M120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O120">
         <v>1.556</v>
       </c>
-      <c r="R120" s="4"/>
-      <c r="S120" s="4"/>
-      <c r="T120" s="4"/>
-      <c r="U120" s="4"/>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="R121" s="4"/>
-      <c r="S121" s="4"/>
-      <c r="T121" s="4"/>
-      <c r="U121" s="4"/>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="R122" s="4"/>
-      <c r="S122" s="4"/>
-      <c r="T122" s="4"/>
-      <c r="U122" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/cyano_atx_24.xlsx
+++ b/data/cyano_atx_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jld/Documents/Github/River_HAB_Modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516D896E-94C5-6040-90A9-0D5214DC8149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0916428D-C709-DE44-AC02-AC5130F9B77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,8 +690,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -751,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -761,6 +763,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1068,6 +1076,7 @@
   <dimension ref="A1:U120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="8.83203125" style="6"/>
     <col min="21" max="21" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1078,7 +1087,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1128,7 +1137,7 @@
       <c r="B2" t="s">
         <v>134</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>179</v>
       </c>
       <c r="D2" t="s">
@@ -1176,7 +1185,7 @@
       <c r="B3" t="s">
         <v>135</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>179</v>
       </c>
       <c r="D3" t="s">
@@ -1223,7 +1232,7 @@
       <c r="B4" t="s">
         <v>136</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>179</v>
       </c>
       <c r="D4" t="s">
@@ -1270,7 +1279,7 @@
       <c r="B5" t="s">
         <v>137</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D5" t="s">
@@ -1317,7 +1326,7 @@
       <c r="B6" t="s">
         <v>138</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D6" t="s">
@@ -1364,7 +1373,7 @@
       <c r="B7" t="s">
         <v>139</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D7" t="s">
@@ -1411,7 +1420,7 @@
       <c r="B8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D8" t="s">
@@ -1458,7 +1467,7 @@
       <c r="B9" t="s">
         <v>141</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="8" t="s">
         <v>181</v>
       </c>
       <c r="D9" t="s">
@@ -1505,7 +1514,7 @@
       <c r="B10" t="s">
         <v>142</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="8" t="s">
         <v>181</v>
       </c>
       <c r="D10" t="s">
@@ -1552,7 +1561,7 @@
       <c r="B11" t="s">
         <v>143</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D11" t="s">
@@ -1599,7 +1608,7 @@
       <c r="B12" t="s">
         <v>144</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D12" t="s">
@@ -1646,7 +1655,7 @@
       <c r="B13" t="s">
         <v>145</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D13" t="s">
@@ -1693,7 +1702,7 @@
       <c r="B14" t="s">
         <v>146</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D14" t="s">
@@ -1740,7 +1749,7 @@
       <c r="B15" t="s">
         <v>147</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="8" t="s">
         <v>183</v>
       </c>
       <c r="D15" t="s">
@@ -1787,7 +1796,7 @@
       <c r="B16" t="s">
         <v>148</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="8" t="s">
         <v>183</v>
       </c>
       <c r="D16" t="s">
@@ -1834,7 +1843,7 @@
       <c r="B17" t="s">
         <v>149</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="8" t="s">
         <v>184</v>
       </c>
       <c r="D17" t="s">
@@ -1881,7 +1890,7 @@
       <c r="B18" t="s">
         <v>149</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D18" t="s">
@@ -1928,7 +1937,7 @@
       <c r="B19" t="s">
         <v>149</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D19" t="s">
@@ -1975,7 +1984,7 @@
       <c r="B20" t="s">
         <v>150</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D20" t="s">
@@ -2022,7 +2031,7 @@
       <c r="B21" t="s">
         <v>151</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D21" t="s">
@@ -2069,7 +2078,7 @@
       <c r="B22" t="s">
         <v>152</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D22" t="s">
@@ -2116,7 +2125,7 @@
       <c r="B23" t="s">
         <v>150</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D23" t="s">
@@ -2163,7 +2172,7 @@
       <c r="B24" t="s">
         <v>151</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D24" t="s">
@@ -2210,7 +2219,7 @@
       <c r="B25" t="s">
         <v>152</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D25" t="s">
@@ -2257,7 +2266,7 @@
       <c r="B26" t="s">
         <v>153</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D26" t="s">
@@ -2304,7 +2313,7 @@
       <c r="B27" t="s">
         <v>154</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>185</v>
       </c>
       <c r="D27" t="s">
@@ -2351,7 +2360,7 @@
       <c r="B28" t="s">
         <v>154</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>185</v>
       </c>
       <c r="D28" t="s">
@@ -2398,7 +2407,7 @@
       <c r="B29" t="s">
         <v>155</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>185</v>
       </c>
       <c r="D29" t="s">
@@ -2445,7 +2454,7 @@
       <c r="B30" t="s">
         <v>155</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>185</v>
       </c>
       <c r="D30" t="s">
@@ -2492,7 +2501,7 @@
       <c r="B31" t="s">
         <v>149</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D31" t="s">
@@ -2539,7 +2548,7 @@
       <c r="B32" t="s">
         <v>149</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D32" t="s">
@@ -2586,7 +2595,7 @@
       <c r="B33" t="s">
         <v>156</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D33" t="s">
@@ -2633,7 +2642,7 @@
       <c r="B34" t="s">
         <v>157</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D34" t="s">
@@ -2680,7 +2689,7 @@
       <c r="B35" t="s">
         <v>149</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D35" t="s">
@@ -2727,7 +2736,7 @@
       <c r="B36" t="s">
         <v>150</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D36" t="s">
@@ -2774,7 +2783,7 @@
       <c r="B37" t="s">
         <v>150</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D37" t="s">
@@ -2821,7 +2830,7 @@
       <c r="B38" t="s">
         <v>154</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D38" t="s">
@@ -2868,7 +2877,7 @@
       <c r="B39" t="s">
         <v>154</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D39" t="s">
@@ -2915,7 +2924,7 @@
       <c r="B40" t="s">
         <v>155</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D40" t="s">
@@ -2962,7 +2971,7 @@
       <c r="B41" t="s">
         <v>155</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D41" t="s">
@@ -3009,7 +3018,7 @@
       <c r="B42" t="s">
         <v>149</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D42" t="s">
@@ -3056,7 +3065,7 @@
       <c r="B43" t="s">
         <v>158</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D43" t="s">
@@ -3103,7 +3112,7 @@
       <c r="B44" t="s">
         <v>149</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D44" t="s">
@@ -3150,7 +3159,7 @@
       <c r="B45" t="s">
         <v>158</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D45" t="s">
@@ -3197,7 +3206,7 @@
       <c r="B46" t="s">
         <v>159</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D46" t="s">
@@ -3244,7 +3253,7 @@
       <c r="B47" t="s">
         <v>150</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D47" t="s">
@@ -3291,7 +3300,7 @@
       <c r="B48" t="s">
         <v>150</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D48" t="s">
@@ -3338,7 +3347,7 @@
       <c r="B49" t="s">
         <v>154</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D49" t="s">
@@ -3385,7 +3394,7 @@
       <c r="B50" t="s">
         <v>154</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D50" t="s">
@@ -3432,7 +3441,7 @@
       <c r="B51" t="s">
         <v>155</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D51" t="s">
@@ -3479,7 +3488,7 @@
       <c r="B52" t="s">
         <v>160</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D52" t="s">
@@ -3526,7 +3535,7 @@
       <c r="B53" t="s">
         <v>161</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D53" t="s">
@@ -3573,7 +3582,7 @@
       <c r="B54" t="s">
         <v>155</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D54" t="s">
@@ -3620,7 +3629,7 @@
       <c r="B55" t="s">
         <v>160</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D55" t="s">
@@ -3667,7 +3676,7 @@
       <c r="B56" t="s">
         <v>161</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="7" t="s">
         <v>188</v>
       </c>
       <c r="D56" t="s">
@@ -3714,7 +3723,7 @@
       <c r="B57" t="s">
         <v>148</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="7" t="s">
         <v>189</v>
       </c>
       <c r="D57" t="s">
@@ -3761,7 +3770,7 @@
       <c r="B58" t="s">
         <v>136</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="7" t="s">
         <v>189</v>
       </c>
       <c r="D58" t="s">
@@ -3808,7 +3817,7 @@
       <c r="B59" t="s">
         <v>146</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="7" t="s">
         <v>189</v>
       </c>
       <c r="D59" t="s">
@@ -3855,7 +3864,7 @@
       <c r="B60" t="s">
         <v>162</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="7" t="s">
         <v>189</v>
       </c>
       <c r="D60" t="s">
@@ -3902,7 +3911,7 @@
       <c r="B61" t="s">
         <v>145</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="7" t="s">
         <v>190</v>
       </c>
       <c r="D61" t="s">
@@ -3949,7 +3958,7 @@
       <c r="B62" t="s">
         <v>163</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="7" t="s">
         <v>190</v>
       </c>
       <c r="D62" t="s">
@@ -3996,7 +4005,7 @@
       <c r="B63" t="s">
         <v>147</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="7" t="s">
         <v>190</v>
       </c>
       <c r="D63" t="s">
@@ -4043,7 +4052,7 @@
       <c r="B64" t="s">
         <v>142</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="7" t="s">
         <v>191</v>
       </c>
       <c r="D64" t="s">
@@ -4090,7 +4099,7 @@
       <c r="B65" t="s">
         <v>134</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="7" t="s">
         <v>192</v>
       </c>
       <c r="D65" t="s">
@@ -4137,7 +4146,7 @@
       <c r="B66" t="s">
         <v>140</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="7" t="s">
         <v>193</v>
       </c>
       <c r="D66" t="s">
@@ -4184,7 +4193,7 @@
       <c r="B67" t="s">
         <v>164</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="7" t="s">
         <v>193</v>
       </c>
       <c r="D67" t="s">
@@ -4231,7 +4240,7 @@
       <c r="B68" t="s">
         <v>144</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="7" t="s">
         <v>194</v>
       </c>
       <c r="D68" t="s">
@@ -4278,7 +4287,7 @@
       <c r="B69" t="s">
         <v>147</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D69" t="s">
@@ -4325,7 +4334,7 @@
       <c r="B70" t="s">
         <v>145</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D70" t="s">
@@ -4372,7 +4381,7 @@
       <c r="B71" t="s">
         <v>165</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D71" t="s">
@@ -4419,7 +4428,7 @@
       <c r="B72" t="s">
         <v>149</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D72" t="s">
@@ -4466,7 +4475,7 @@
       <c r="B73" t="s">
         <v>149</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D73" t="s">
@@ -4513,7 +4522,7 @@
       <c r="B74" t="s">
         <v>150</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D74" t="s">
@@ -4560,7 +4569,7 @@
       <c r="B75" t="s">
         <v>150</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D75" t="s">
@@ -4607,7 +4616,7 @@
       <c r="B76" t="s">
         <v>154</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D76" t="s">
@@ -4654,7 +4663,7 @@
       <c r="B77" t="s">
         <v>166</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D77" t="s">
@@ -4701,7 +4710,7 @@
       <c r="B78" t="s">
         <v>167</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D78" t="s">
@@ -4748,7 +4757,7 @@
       <c r="B79" t="s">
         <v>168</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D79" t="s">
@@ -4795,7 +4804,7 @@
       <c r="B80" t="s">
         <v>155</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D80" t="s">
@@ -4842,7 +4851,7 @@
       <c r="B81" t="s">
         <v>155</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D81" t="s">
@@ -4889,7 +4898,7 @@
       <c r="B82" t="s">
         <v>139</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="7" t="s">
         <v>197</v>
       </c>
       <c r="D82" t="s">
@@ -4936,7 +4945,7 @@
       <c r="B83" t="s">
         <v>138</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="7" t="s">
         <v>197</v>
       </c>
       <c r="D83" t="s">
@@ -4983,7 +4992,7 @@
       <c r="B84" t="s">
         <v>136</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="7" t="s">
         <v>197</v>
       </c>
       <c r="D84" t="s">
@@ -5030,7 +5039,7 @@
       <c r="B85" t="s">
         <v>143</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="7" t="s">
         <v>198</v>
       </c>
       <c r="D85" t="s">
@@ -5077,7 +5086,7 @@
       <c r="B86" t="s">
         <v>145</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="7" t="s">
         <v>198</v>
       </c>
       <c r="D86" t="s">
@@ -5124,7 +5133,7 @@
       <c r="B87" t="s">
         <v>148</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="7" t="s">
         <v>199</v>
       </c>
       <c r="D87" t="s">
@@ -5171,7 +5180,7 @@
       <c r="B88" t="s">
         <v>141</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="7" t="s">
         <v>199</v>
       </c>
       <c r="D88" t="s">
@@ -5218,7 +5227,7 @@
       <c r="B89" t="s">
         <v>149</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D89" t="s">
@@ -5265,7 +5274,7 @@
       <c r="B90" t="s">
         <v>150</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D90" t="s">
@@ -5312,7 +5321,7 @@
       <c r="B91" t="s">
         <v>151</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D91" t="s">
@@ -5359,7 +5368,7 @@
       <c r="B92" t="s">
         <v>169</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D92" t="s">
@@ -5406,7 +5415,7 @@
       <c r="B93" t="s">
         <v>154</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D93" t="s">
@@ -5453,7 +5462,7 @@
       <c r="B94" t="s">
         <v>155</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="7" t="s">
         <v>200</v>
       </c>
       <c r="D94" t="s">
@@ -5500,7 +5509,7 @@
       <c r="B95" t="s">
         <v>149</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D95" t="s">
@@ -5547,7 +5556,7 @@
       <c r="B96" t="s">
         <v>156</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D96" t="s">
@@ -5594,7 +5603,7 @@
       <c r="B97" t="s">
         <v>157</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D97" t="s">
@@ -5641,7 +5650,7 @@
       <c r="B98" t="s">
         <v>150</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D98" t="s">
@@ -5688,7 +5697,7 @@
       <c r="B99" t="s">
         <v>154</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D99" t="s">
@@ -5735,7 +5744,7 @@
       <c r="B100" t="s">
         <v>155</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D100" t="s">
@@ -5782,7 +5791,7 @@
       <c r="B101" t="s">
         <v>149</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="7" t="s">
         <v>184</v>
       </c>
       <c r="D101" t="s">
@@ -5829,7 +5838,7 @@
       <c r="B102" t="s">
         <v>146</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="7" t="s">
         <v>202</v>
       </c>
       <c r="D102" t="s">
@@ -5876,7 +5885,7 @@
       <c r="B103" t="s">
         <v>148</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="7" t="s">
         <v>202</v>
       </c>
       <c r="D103" t="s">
@@ -5923,7 +5932,7 @@
       <c r="B104" t="s">
         <v>141</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="7" t="s">
         <v>203</v>
       </c>
       <c r="D104" t="s">
@@ -5970,7 +5979,7 @@
       <c r="B105" t="s">
         <v>138</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="7" t="s">
         <v>204</v>
       </c>
       <c r="D105" t="s">
@@ -6017,7 +6026,7 @@
       <c r="B106" t="s">
         <v>139</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="7" t="s">
         <v>204</v>
       </c>
       <c r="D106" t="s">
@@ -6064,7 +6073,7 @@
       <c r="B107" t="s">
         <v>136</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="7" t="s">
         <v>204</v>
       </c>
       <c r="D107" t="s">
@@ -6111,7 +6120,7 @@
       <c r="B108" t="s">
         <v>143</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="7" t="s">
         <v>202</v>
       </c>
       <c r="D108" t="s">
@@ -6158,7 +6167,7 @@
       <c r="B109" t="s">
         <v>170</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="7" t="s">
         <v>205</v>
       </c>
       <c r="D109" t="s">
@@ -6205,7 +6214,7 @@
       <c r="B110" t="s">
         <v>171</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="7" t="s">
         <v>205</v>
       </c>
       <c r="D110" t="s">
@@ -6252,7 +6261,7 @@
       <c r="B111" t="s">
         <v>172</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="7" t="s">
         <v>205</v>
       </c>
       <c r="D111" t="s">
@@ -6299,7 +6308,7 @@
       <c r="B112" t="s">
         <v>149</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="7" t="s">
         <v>206</v>
       </c>
       <c r="D112" t="s">
@@ -6346,7 +6355,7 @@
       <c r="B113" t="s">
         <v>149</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D113" t="s">
@@ -6393,7 +6402,7 @@
       <c r="B114" t="s">
         <v>155</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D114" t="s">
@@ -6440,7 +6449,7 @@
       <c r="B115" t="s">
         <v>173</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D115" t="s">
@@ -6487,7 +6496,7 @@
       <c r="B116" t="s">
         <v>174</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D116" t="s">
@@ -6534,7 +6543,7 @@
       <c r="B117" t="s">
         <v>175</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D117" t="s">
@@ -6581,7 +6590,7 @@
       <c r="B118" t="s">
         <v>176</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D118" t="s">
@@ -6628,7 +6637,7 @@
       <c r="B119" t="s">
         <v>177</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D119" t="s">
@@ -6675,7 +6684,7 @@
       <c r="B120" t="s">
         <v>178</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D120" t="s">

--- a/data/cyano_atx_24.xlsx
+++ b/data/cyano_atx_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jld/Documents/Github/River_HAB_Modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0916428D-C709-DE44-AC02-AC5130F9B77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1D7D62-0E10-CB43-A137-F59A8E84EEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="219">
   <si>
     <t>ESF</t>
   </si>
@@ -659,12 +659,6 @@
     <t>6/19/2024</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>nd</t>
   </si>
   <si>
@@ -684,6 +678,18 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>TAC</t>
   </si>
 </sst>
 </file>
@@ -692,10 +698,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -717,6 +723,11 @@
       <name val="Courier New"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -726,7 +737,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -749,11 +760,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -763,12 +783,16 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1126,6 +1150,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="Q1" s="10"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="U1" s="3"/>
@@ -1140,45 +1165,47 @@
       <c r="C2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D2" t="s">
-        <v>208</v>
+      <c r="D2" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2">
         <v>0.113</v>
       </c>
       <c r="G2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H2">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J2">
         <v>0.05</v>
       </c>
       <c r="K2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O2" t="s">
-        <v>210</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1188,44 +1215,46 @@
       <c r="C3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D3" t="s">
-        <v>208</v>
+      <c r="D3" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F3">
         <v>0.11899999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H3">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J3">
         <v>0.05</v>
       </c>
       <c r="K3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1235,44 +1264,46 @@
       <c r="C4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D4" t="s">
-        <v>208</v>
+      <c r="D4" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F4">
         <v>0.108</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H4">
         <v>0.09</v>
       </c>
       <c r="I4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J4">
         <v>0.05</v>
       </c>
       <c r="K4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+    </row>
+    <row r="5" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1282,44 +1313,46 @@
       <c r="C5" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D5" t="s">
-        <v>208</v>
+      <c r="D5" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F5">
         <v>0.128</v>
       </c>
       <c r="G5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H5">
         <v>0.106</v>
       </c>
       <c r="I5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J5">
         <v>0.06</v>
       </c>
       <c r="K5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1329,44 +1362,46 @@
       <c r="C6" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D6" t="s">
-        <v>208</v>
+      <c r="D6" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F6">
         <v>0.11899999999999999</v>
       </c>
       <c r="G6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H6">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J6">
         <v>0.05</v>
       </c>
       <c r="K6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+    </row>
+    <row r="7" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1376,8 +1411,8 @@
       <c r="C7" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D7" t="s">
-        <v>208</v>
+      <c r="D7" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E7">
         <v>9.4E-2</v>
@@ -1386,34 +1421,36 @@
         <v>0.114</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H7">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J7">
         <v>0.05</v>
       </c>
       <c r="K7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L7">
         <v>9.4E-2</v>
       </c>
       <c r="M7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O7">
         <v>9.4E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+    </row>
+    <row r="8" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1423,44 +1460,46 @@
       <c r="C8" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D8" t="s">
-        <v>208</v>
+      <c r="D8" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F8">
         <v>0.15</v>
       </c>
       <c r="G8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H8">
         <v>0.124</v>
       </c>
       <c r="I8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J8">
         <v>0.06</v>
       </c>
       <c r="K8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+    </row>
+    <row r="9" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1509,8 @@
       <c r="C9" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D9" t="s">
-        <v>208</v>
+      <c r="D9" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E9">
         <v>0.14399999999999999</v>
@@ -1480,34 +1519,36 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="G9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H9">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J9">
         <v>0.05</v>
       </c>
       <c r="K9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L9">
         <v>0.14399999999999999</v>
       </c>
       <c r="M9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O9">
         <v>0.14399999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+    </row>
+    <row r="10" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1517,8 +1558,8 @@
       <c r="C10" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D10" t="s">
-        <v>208</v>
+      <c r="D10" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="E10">
         <v>0.624</v>
@@ -1527,34 +1568,36 @@
         <v>0.115</v>
       </c>
       <c r="G10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H10">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J10">
         <v>0.05</v>
       </c>
       <c r="K10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L10">
         <v>0.624</v>
       </c>
       <c r="M10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O10">
         <v>0.624</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+    </row>
+    <row r="11" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1564,44 +1607,46 @@
       <c r="C11" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D11" t="s">
-        <v>208</v>
+      <c r="D11" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F11">
         <v>0.158</v>
       </c>
       <c r="G11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H11">
         <v>0.13100000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O11" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+    </row>
+    <row r="12" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1611,44 +1656,46 @@
       <c r="C12" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D12" t="s">
-        <v>208</v>
+      <c r="D12" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F12">
         <v>0.115</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H12">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J12">
         <v>0.05</v>
       </c>
       <c r="K12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1658,44 +1705,46 @@
       <c r="C13" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D13" t="s">
-        <v>208</v>
+      <c r="D13" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F13">
         <v>0.111</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H13">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J13">
         <v>0.05</v>
       </c>
       <c r="K13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+    </row>
+    <row r="14" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1705,44 +1754,46 @@
       <c r="C14" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D14" t="s">
-        <v>208</v>
+      <c r="D14" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F14">
         <v>0.109</v>
       </c>
       <c r="G14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H14">
         <v>0.09</v>
       </c>
       <c r="I14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J14">
         <v>0.05</v>
       </c>
       <c r="K14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O14" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1752,8 +1803,8 @@
       <c r="C15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D15" t="s">
-        <v>208</v>
+      <c r="D15" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E15">
         <v>0.47</v>
@@ -1762,19 +1813,19 @@
         <v>0.112</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H15">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J15">
         <v>0.05</v>
       </c>
       <c r="K15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L15">
         <v>0.11899999999999999</v>
@@ -1788,8 +1839,10 @@
       <c r="O15">
         <v>0.47</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+    </row>
+    <row r="16" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1799,44 +1852,46 @@
       <c r="C16" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D16" t="s">
-        <v>208</v>
+      <c r="D16" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F16">
         <v>0.111</v>
       </c>
       <c r="G16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H16">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="I16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J16">
         <v>0.05</v>
       </c>
       <c r="K16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+    </row>
+    <row r="17" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1846,93 +1901,97 @@
       <c r="C17" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D17" t="s">
-        <v>208</v>
+      <c r="D17" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F17">
         <v>0.121</v>
       </c>
       <c r="G17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H17">
         <v>0.1</v>
       </c>
       <c r="I17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J17">
         <v>0.05</v>
       </c>
       <c r="K17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O17" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+    </row>
+    <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G18" t="s">
+        <v>208</v>
+      </c>
+      <c r="H18">
+        <v>0.1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18">
+        <v>0.05</v>
+      </c>
+      <c r="K18" t="s">
+        <v>208</v>
+      </c>
+      <c r="L18" t="s">
+        <v>208</v>
+      </c>
+      <c r="M18" t="s">
+        <v>208</v>
+      </c>
+      <c r="N18" t="s">
+        <v>208</v>
+      </c>
+      <c r="O18" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+    </row>
+    <row r="19" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" t="s">
-        <v>210</v>
-      </c>
-      <c r="F18">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="G18" t="s">
-        <v>210</v>
-      </c>
-      <c r="H18">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="I18" t="s">
-        <v>210</v>
-      </c>
-      <c r="J18">
-        <v>0.05</v>
-      </c>
-      <c r="K18" t="s">
-        <v>210</v>
-      </c>
-      <c r="L18" t="s">
-        <v>210</v>
-      </c>
-      <c r="M18" t="s">
-        <v>210</v>
-      </c>
-      <c r="N18" t="s">
-        <v>210</v>
-      </c>
-      <c r="O18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>32</v>
       </c>
       <c r="B19" t="s">
         <v>149</v>
@@ -1940,422 +1999,440 @@
       <c r="C19" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E19">
-        <v>2.1999999999999999E-2</v>
+      <c r="D19" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" t="s">
+        <v>208</v>
       </c>
       <c r="F19">
-        <v>0.121</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H19">
-        <v>0.10100000000000001</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J19">
         <v>0.05</v>
       </c>
       <c r="K19" t="s">
-        <v>210</v>
-      </c>
-      <c r="L19">
-        <v>2.1999999999999999E-2</v>
+        <v>208</v>
+      </c>
+      <c r="L19" t="s">
+        <v>208</v>
       </c>
       <c r="M19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s">
-        <v>210</v>
-      </c>
-      <c r="O19">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O19" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+    </row>
+    <row r="20" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" t="s">
-        <v>210</v>
+      <c r="D20" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20">
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="F20">
         <v>0.121</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H20">
         <v>0.10100000000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J20">
         <v>0.05</v>
       </c>
       <c r="K20" t="s">
-        <v>210</v>
-      </c>
-      <c r="L20" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="L20">
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="M20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s">
-        <v>210</v>
-      </c>
-      <c r="O20" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O20">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+    </row>
+    <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D21" t="s">
-        <v>208</v>
-      </c>
-      <c r="E21">
-        <v>9.8000000000000004E-2</v>
+      <c r="D21" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" t="s">
+        <v>208</v>
       </c>
       <c r="F21">
-        <v>0.155</v>
+        <v>0.121</v>
       </c>
       <c r="G21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H21">
-        <v>0.128</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J21">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="K21" t="s">
-        <v>210</v>
-      </c>
-      <c r="L21">
-        <v>9.8000000000000004E-2</v>
+        <v>208</v>
+      </c>
+      <c r="L21" t="s">
+        <v>208</v>
       </c>
       <c r="M21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N21" t="s">
-        <v>210</v>
-      </c>
-      <c r="O21">
-        <v>9.8000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+    </row>
+    <row r="22" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D22" t="s">
-        <v>208</v>
-      </c>
-      <c r="E22" t="s">
-        <v>210</v>
+      <c r="D22" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E22">
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F22">
-        <v>0.14699999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="G22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H22">
-        <v>0.122</v>
+        <v>0.128</v>
       </c>
       <c r="I22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J22">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K22" t="s">
-        <v>210</v>
-      </c>
-      <c r="L22" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="L22">
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="M22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N22" t="s">
-        <v>210</v>
-      </c>
-      <c r="O22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O22">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+    </row>
+    <row r="23" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D23" t="s">
-        <v>208</v>
-      </c>
-      <c r="E23">
-        <v>5.0999999999999997E-2</v>
+      <c r="D23" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" t="s">
+        <v>208</v>
       </c>
       <c r="F23">
-        <v>0.109</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="G23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H23">
-        <v>0.09</v>
+        <v>0.122</v>
       </c>
       <c r="I23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J23">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K23" t="s">
-        <v>210</v>
-      </c>
-      <c r="L23">
-        <v>5.0999999999999997E-2</v>
+        <v>208</v>
+      </c>
+      <c r="L23" t="s">
+        <v>208</v>
       </c>
       <c r="M23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s">
-        <v>210</v>
-      </c>
-      <c r="O23">
-        <v>5.0999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O23" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+    </row>
+    <row r="24" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D24" t="s">
-        <v>208</v>
+      <c r="D24" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E24">
-        <v>6.4000000000000001E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="F24">
-        <v>0.13300000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="G24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H24">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="I24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J24">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L24">
-        <v>6.4000000000000001E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="M24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O24">
-        <v>6.4000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+    </row>
+    <row r="25" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D25" t="s">
-        <v>208</v>
+      <c r="D25" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E25">
-        <v>0.10199999999999999</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="F25">
-        <v>0.13100000000000001</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H25">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="I25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J25">
         <v>0.06</v>
       </c>
       <c r="K25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L25">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="M25" t="s">
+        <v>208</v>
+      </c>
+      <c r="N25" t="s">
+        <v>208</v>
+      </c>
+      <c r="O25">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+    </row>
+    <row r="26" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26">
         <v>0.10199999999999999</v>
       </c>
-      <c r="M25" t="s">
-        <v>210</v>
-      </c>
-      <c r="N25" t="s">
-        <v>210</v>
-      </c>
-      <c r="O25">
+      <c r="F26">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="G26" t="s">
+        <v>208</v>
+      </c>
+      <c r="H26">
+        <v>0.109</v>
+      </c>
+      <c r="I26" t="s">
+        <v>208</v>
+      </c>
+      <c r="J26">
+        <v>0.06</v>
+      </c>
+      <c r="K26" t="s">
+        <v>208</v>
+      </c>
+      <c r="L26">
         <v>0.10199999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="M26" t="s">
+        <v>208</v>
+      </c>
+      <c r="N26" t="s">
+        <v>208</v>
+      </c>
+      <c r="O26">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+    </row>
+    <row r="27" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>39</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D26" t="s">
-        <v>209</v>
-      </c>
-      <c r="E26" t="s">
-        <v>210</v>
-      </c>
-      <c r="F26">
+      <c r="D27" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27">
         <v>3.39</v>
       </c>
-      <c r="G26" t="s">
-        <v>210</v>
-      </c>
-      <c r="H26">
+      <c r="G27" t="s">
+        <v>208</v>
+      </c>
+      <c r="H27">
         <v>1.9370000000000001</v>
       </c>
-      <c r="I26" t="s">
-        <v>210</v>
-      </c>
-      <c r="J26">
+      <c r="I27" t="s">
+        <v>208</v>
+      </c>
+      <c r="J27">
         <v>1.01</v>
       </c>
-      <c r="K26" t="s">
-        <v>210</v>
-      </c>
-      <c r="L26" t="s">
-        <v>210</v>
-      </c>
-      <c r="M26" t="s">
-        <v>210</v>
-      </c>
-      <c r="N26" t="s">
-        <v>210</v>
-      </c>
-      <c r="O26" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="K27" t="s">
+        <v>208</v>
+      </c>
+      <c r="L27" t="s">
+        <v>208</v>
+      </c>
+      <c r="M27" t="s">
+        <v>208</v>
+      </c>
+      <c r="N27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O27" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+    </row>
+    <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>40</v>
-      </c>
-      <c r="B27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="F27">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="G27" t="s">
-        <v>210</v>
-      </c>
-      <c r="H27">
-        <v>9.1999999999999998E-2</v>
-      </c>
-      <c r="I27" t="s">
-        <v>210</v>
-      </c>
-      <c r="J27">
-        <v>0.05</v>
-      </c>
-      <c r="K27" t="s">
-        <v>210</v>
-      </c>
-      <c r="L27">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="M27" t="s">
-        <v>210</v>
-      </c>
-      <c r="N27" t="s">
-        <v>210</v>
-      </c>
-      <c r="O27">
-        <v>9.6000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>41</v>
       </c>
       <c r="B28" t="s">
         <v>154</v>
@@ -2363,93 +2440,97 @@
       <c r="C28" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D28" t="s">
-        <v>208</v>
+      <c r="D28" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E28">
-        <v>0.158</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F28">
-        <v>0.17199999999999999</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H28">
-        <v>9.8000000000000004E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="I28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J28">
         <v>0.05</v>
       </c>
       <c r="K28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L28">
-        <v>0.158</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="M28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O28">
-        <v>0.158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+    </row>
+    <row r="29" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D29" t="s">
-        <v>208</v>
+      <c r="D29" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E29">
-        <v>8.5999999999999993E-2</v>
+        <v>0.158</v>
       </c>
       <c r="F29">
-        <v>0.21</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="G29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H29">
-        <v>0.12</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J29">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L29">
-        <v>8.5999999999999993E-2</v>
+        <v>0.158</v>
       </c>
       <c r="M29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O29">
-        <v>8.5999999999999993E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.158</v>
+      </c>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+    </row>
+    <row r="30" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>155</v>
@@ -2457,93 +2538,97 @@
       <c r="C30" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D30" t="s">
-        <v>208</v>
+      <c r="D30" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E30">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="F30">
+        <v>0.21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>208</v>
+      </c>
+      <c r="H30">
+        <v>0.12</v>
+      </c>
+      <c r="I30" t="s">
+        <v>208</v>
+      </c>
+      <c r="J30">
+        <v>0.06</v>
+      </c>
+      <c r="K30" t="s">
+        <v>208</v>
+      </c>
+      <c r="L30">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="M30" t="s">
+        <v>208</v>
+      </c>
+      <c r="N30" t="s">
+        <v>208</v>
+      </c>
+      <c r="O30">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+    </row>
+    <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>0.17699999999999999</v>
       </c>
-      <c r="G30" t="s">
-        <v>210</v>
-      </c>
-      <c r="H30">
+      <c r="G31" t="s">
+        <v>208</v>
+      </c>
+      <c r="H31">
         <v>0.10100000000000001</v>
       </c>
-      <c r="I30" t="s">
-        <v>210</v>
-      </c>
-      <c r="J30">
-        <v>0.05</v>
-      </c>
-      <c r="K30" t="s">
-        <v>210</v>
-      </c>
-      <c r="L30">
+      <c r="I31" t="s">
+        <v>208</v>
+      </c>
+      <c r="J31">
+        <v>0.05</v>
+      </c>
+      <c r="K31" t="s">
+        <v>208</v>
+      </c>
+      <c r="L31">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="M30" t="s">
-        <v>210</v>
-      </c>
-      <c r="N30" t="s">
-        <v>210</v>
-      </c>
-      <c r="O30">
+      <c r="M31" t="s">
+        <v>208</v>
+      </c>
+      <c r="N31" t="s">
+        <v>208</v>
+      </c>
+      <c r="O31">
         <v>6.6000000000000003E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+    </row>
+    <row r="32" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>44</v>
-      </c>
-      <c r="B31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" t="s">
-        <v>208</v>
-      </c>
-      <c r="E31">
-        <v>2.5310000000000001</v>
-      </c>
-      <c r="F31">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="G31" t="s">
-        <v>210</v>
-      </c>
-      <c r="H31">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="I31" t="s">
-        <v>210</v>
-      </c>
-      <c r="J31">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K31">
-        <v>2.0640000000000001</v>
-      </c>
-      <c r="L31">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="M31" t="s">
-        <v>210</v>
-      </c>
-      <c r="N31" t="s">
-        <v>210</v>
-      </c>
-      <c r="O31">
-        <v>2.5310000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>45</v>
       </c>
       <c r="B32" t="s">
         <v>149</v>
@@ -2551,234 +2636,244 @@
       <c r="C32" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D32" t="s">
-        <v>208</v>
+      <c r="D32" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E32">
-        <v>0.47499999999999998</v>
+        <v>2.5310000000000001</v>
       </c>
       <c r="F32">
-        <v>0.159</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="G32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H32">
-        <v>9.0999999999999998E-2</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="I32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J32">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K32">
-        <v>0.43</v>
+        <v>2.0640000000000001</v>
       </c>
       <c r="L32">
-        <v>4.4999999999999998E-2</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="M32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O32">
-        <v>0.47499999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+        <v>2.5310000000000001</v>
+      </c>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+    </row>
+    <row r="33" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D33" t="s">
-        <v>208</v>
+      <c r="D33" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E33">
-        <v>0.47099999999999997</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F33">
-        <v>0.214</v>
+        <v>0.159</v>
       </c>
       <c r="G33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H33">
-        <v>0.122</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="I33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J33">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K33">
-        <v>0.41799999999999998</v>
+        <v>0.43</v>
       </c>
       <c r="L33">
-        <v>5.2999999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="M33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O33">
-        <v>0.47099999999999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+    </row>
+    <row r="34" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D34" t="s">
-        <v>208</v>
+      <c r="D34" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E34">
-        <v>0.66800000000000004</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="F34">
-        <v>0.17299999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="G34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H34">
-        <v>9.9000000000000005E-2</v>
+        <v>0.122</v>
       </c>
       <c r="I34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J34">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K34">
-        <v>0.497</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="L34">
-        <v>0.17100000000000001</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="M34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O34">
-        <v>0.66800000000000004</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+    </row>
+    <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D35" t="s">
-        <v>208</v>
+      <c r="D35" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E35">
-        <v>2.4969999999999999</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="F35">
-        <v>0.17</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="G35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H35">
-        <v>9.7000000000000003E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J35">
         <v>0.05</v>
       </c>
       <c r="K35">
-        <v>1.901</v>
+        <v>0.497</v>
       </c>
       <c r="L35">
-        <v>0.59599999999999997</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="M35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O35">
-        <v>2.4969999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+    </row>
+    <row r="36" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D36" t="s">
-        <v>208</v>
+      <c r="D36" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E36">
-        <v>0.59399999999999997</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="F36">
-        <v>0.17399999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H36">
-        <v>9.9000000000000005E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J36">
         <v>0.05</v>
       </c>
       <c r="K36">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="L36" t="s">
-        <v>210</v>
+        <v>1.901</v>
+      </c>
+      <c r="L36">
+        <v>0.59599999999999997</v>
       </c>
       <c r="M36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O36">
-        <v>0.59399999999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+        <v>2.4969999999999999</v>
+      </c>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+    </row>
+    <row r="37" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
         <v>150</v>
@@ -2786,93 +2881,97 @@
       <c r="C37" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D37" t="s">
-        <v>208</v>
+      <c r="D37" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E37">
-        <v>0.29799999999999999</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="F37">
-        <v>0.19900000000000001</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H37">
-        <v>0.114</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J37">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K37">
-        <v>0.20399999999999999</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="L37" t="s">
-        <v>215</v>
-      </c>
-      <c r="M37">
-        <v>9.2999999999999999E-2</v>
+        <v>208</v>
+      </c>
+      <c r="M37" t="s">
+        <v>208</v>
       </c>
       <c r="N37" t="s">
-        <v>215</v>
-      </c>
-      <c r="O37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O37">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+    </row>
+    <row r="38" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D38" t="s">
-        <v>208</v>
+      <c r="D38" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E38">
-        <v>8.1000000000000003E-2</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="F38">
-        <v>0.16900000000000001</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="G38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H38">
-        <v>9.7000000000000003E-2</v>
+        <v>0.114</v>
       </c>
       <c r="I38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J38">
-        <v>0.05</v>
-      </c>
-      <c r="K38" t="s">
-        <v>210</v>
-      </c>
-      <c r="L38">
-        <v>8.1000000000000003E-2</v>
-      </c>
-      <c r="M38" t="s">
-        <v>210</v>
+        <v>0.06</v>
+      </c>
+      <c r="K38">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="L38" t="s">
+        <v>213</v>
+      </c>
+      <c r="M38">
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="N38" t="s">
-        <v>210</v>
-      </c>
-      <c r="O38">
-        <v>8.1000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="O38" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+    </row>
+    <row r="39" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
         <v>154</v>
@@ -2880,93 +2979,97 @@
       <c r="C39" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D39" t="s">
-        <v>208</v>
-      </c>
-      <c r="E39" t="s">
-        <v>210</v>
+      <c r="D39" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39">
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="F39">
-        <v>0.30099999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="G39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H39">
-        <v>0.17199999999999999</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J39">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="K39" t="s">
-        <v>210</v>
-      </c>
-      <c r="L39" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="L39">
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="M39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N39" t="s">
-        <v>210</v>
-      </c>
-      <c r="O39" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O39">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+    </row>
+    <row r="40" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D40" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40">
-        <v>0.88</v>
+      <c r="D40" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" t="s">
+        <v>208</v>
       </c>
       <c r="F40">
-        <v>0.18099999999999999</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="G40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H40">
-        <v>0.10299999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="I40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J40">
-        <v>0.05</v>
-      </c>
-      <c r="K40">
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="L40">
-        <v>0.26600000000000001</v>
+        <v>0.09</v>
+      </c>
+      <c r="K40" t="s">
+        <v>208</v>
+      </c>
+      <c r="L40" t="s">
+        <v>208</v>
       </c>
       <c r="M40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N40" t="s">
-        <v>210</v>
-      </c>
-      <c r="O40">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O40" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+    </row>
+    <row r="41" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
         <v>155</v>
@@ -2974,328 +3077,342 @@
       <c r="C41" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D41" t="s">
-        <v>208</v>
+      <c r="D41" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E41">
+        <v>0.88</v>
+      </c>
+      <c r="F41">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="G41" t="s">
+        <v>208</v>
+      </c>
+      <c r="H41">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J41">
+        <v>0.05</v>
+      </c>
+      <c r="K41">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="L41">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="M41" t="s">
+        <v>208</v>
+      </c>
+      <c r="N41" t="s">
+        <v>208</v>
+      </c>
+      <c r="O41">
+        <v>0.88</v>
+      </c>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+    </row>
+    <row r="42" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42">
         <v>1.988</v>
       </c>
-      <c r="F41">
+      <c r="F42">
         <v>0.17499999999999999</v>
       </c>
-      <c r="G41" t="s">
-        <v>210</v>
-      </c>
-      <c r="H41">
+      <c r="G42" t="s">
+        <v>208</v>
+      </c>
+      <c r="H42">
         <v>0.1</v>
       </c>
-      <c r="I41" t="s">
-        <v>210</v>
-      </c>
-      <c r="J41">
-        <v>0.05</v>
-      </c>
-      <c r="K41">
+      <c r="I42" t="s">
+        <v>208</v>
+      </c>
+      <c r="J42">
+        <v>0.05</v>
+      </c>
+      <c r="K42">
         <v>1.218</v>
       </c>
-      <c r="L41">
+      <c r="L42">
         <v>0.77</v>
       </c>
-      <c r="M41" t="s">
-        <v>210</v>
-      </c>
-      <c r="N41" t="s">
-        <v>210</v>
-      </c>
-      <c r="O41">
+      <c r="M42" t="s">
+        <v>208</v>
+      </c>
+      <c r="N42" t="s">
+        <v>208</v>
+      </c>
+      <c r="O42">
         <v>1.988</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+    </row>
+    <row r="43" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>55</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>149</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" t="s">
-        <v>208</v>
-      </c>
-      <c r="E42">
-        <v>0.76</v>
-      </c>
-      <c r="F42">
-        <v>0.16300000000000001</v>
-      </c>
-      <c r="G42" t="s">
-        <v>210</v>
-      </c>
-      <c r="H42">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="I42" t="s">
-        <v>210</v>
-      </c>
-      <c r="J42">
-        <v>0.05</v>
-      </c>
-      <c r="K42">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="L42">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="M42" t="s">
-        <v>210</v>
-      </c>
-      <c r="N42" t="s">
-        <v>210</v>
-      </c>
-      <c r="O42">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" t="s">
-        <v>158</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D43" t="s">
-        <v>208</v>
+      <c r="D43" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E43">
-        <v>0.64300000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="F43">
-        <v>0.18</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="G43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H43">
-        <v>0.10299999999999999</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="I43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J43">
         <v>0.05</v>
       </c>
       <c r="K43">
-        <v>0.54100000000000004</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="L43">
-        <v>0.10199999999999999</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="M43" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N43" t="s">
-        <v>210</v>
-      </c>
-      <c r="O43" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O43">
+        <v>0.76</v>
+      </c>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+    </row>
+    <row r="44" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D44" t="s">
-        <v>208</v>
+      <c r="D44" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E44">
-        <v>6.0549999999999997</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="F44">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H44">
-        <v>9.7000000000000003E-2</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="I44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J44">
         <v>0.05</v>
       </c>
       <c r="K44">
-        <v>5.42</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="L44">
-        <v>0.63500000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="M44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N44" t="s">
-        <v>210</v>
-      </c>
-      <c r="O44">
-        <v>6.0549999999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O44" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+    </row>
+    <row r="45" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D45" t="s">
-        <v>208</v>
+      <c r="D45" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E45">
+        <v>6.0549999999999997</v>
+      </c>
+      <c r="F45">
+        <v>0.17</v>
+      </c>
+      <c r="G45" t="s">
+        <v>208</v>
+      </c>
+      <c r="H45">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>208</v>
+      </c>
+      <c r="J45">
+        <v>0.05</v>
+      </c>
+      <c r="K45">
+        <v>5.42</v>
+      </c>
+      <c r="L45">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="M45" t="s">
+        <v>208</v>
+      </c>
+      <c r="N45" t="s">
+        <v>208</v>
+      </c>
+      <c r="O45">
+        <v>6.0549999999999997</v>
+      </c>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+    </row>
+    <row r="46" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46">
         <v>5.2670000000000003</v>
       </c>
-      <c r="F45">
+      <c r="F46">
         <v>0.183</v>
       </c>
-      <c r="G45" t="s">
-        <v>210</v>
-      </c>
-      <c r="H45">
+      <c r="G46" t="s">
+        <v>208</v>
+      </c>
+      <c r="H46">
         <v>0.105</v>
       </c>
-      <c r="I45" t="s">
-        <v>210</v>
-      </c>
-      <c r="J45">
-        <v>0.05</v>
-      </c>
-      <c r="K45" t="s">
-        <v>210</v>
-      </c>
-      <c r="L45" t="s">
-        <v>210</v>
-      </c>
-      <c r="M45" t="s">
-        <v>210</v>
-      </c>
-      <c r="N45" t="s">
-        <v>210</v>
-      </c>
-      <c r="O45" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="I46" t="s">
+        <v>208</v>
+      </c>
+      <c r="J46">
+        <v>0.05</v>
+      </c>
+      <c r="K46" t="s">
+        <v>208</v>
+      </c>
+      <c r="L46" t="s">
+        <v>208</v>
+      </c>
+      <c r="M46" t="s">
+        <v>208</v>
+      </c>
+      <c r="N46" t="s">
+        <v>208</v>
+      </c>
+      <c r="O46" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+    </row>
+    <row r="47" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>59</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D46" t="s">
-        <v>209</v>
-      </c>
-      <c r="E46" t="s">
-        <v>210</v>
-      </c>
-      <c r="F46">
+      <c r="D47" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47">
         <v>3.39</v>
       </c>
-      <c r="G46" t="s">
-        <v>210</v>
-      </c>
-      <c r="H46">
+      <c r="G47" t="s">
+        <v>208</v>
+      </c>
+      <c r="H47">
         <v>1.9370000000000001</v>
       </c>
-      <c r="I46" t="s">
-        <v>210</v>
-      </c>
-      <c r="J46">
+      <c r="I47" t="s">
+        <v>208</v>
+      </c>
+      <c r="J47">
         <v>1.01</v>
       </c>
-      <c r="K46" t="s">
-        <v>210</v>
-      </c>
-      <c r="L46" t="s">
-        <v>210</v>
-      </c>
-      <c r="M46" t="s">
-        <v>210</v>
-      </c>
-      <c r="N46" t="s">
-        <v>210</v>
-      </c>
-      <c r="O46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="K47" t="s">
+        <v>208</v>
+      </c>
+      <c r="L47" t="s">
+        <v>208</v>
+      </c>
+      <c r="M47" t="s">
+        <v>208</v>
+      </c>
+      <c r="N47" t="s">
+        <v>208</v>
+      </c>
+      <c r="O47" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+    </row>
+    <row r="48" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>60</v>
-      </c>
-      <c r="B47" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D47" t="s">
-        <v>208</v>
-      </c>
-      <c r="E47">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="F47">
-        <v>0.16</v>
-      </c>
-      <c r="G47" t="s">
-        <v>210</v>
-      </c>
-      <c r="H47">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="I47" t="s">
-        <v>210</v>
-      </c>
-      <c r="J47">
-        <v>0.05</v>
-      </c>
-      <c r="K47">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="L47" t="s">
-        <v>215</v>
-      </c>
-      <c r="M47" t="s">
-        <v>210</v>
-      </c>
-      <c r="N47" t="s">
-        <v>210</v>
-      </c>
-      <c r="O47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>61</v>
       </c>
       <c r="B48" t="s">
         <v>150</v>
@@ -3303,93 +3420,97 @@
       <c r="C48" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D48" t="s">
-        <v>208</v>
+      <c r="D48" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E48">
-        <v>4.8780000000000001</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F48">
-        <v>0.16400000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="G48" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H48">
-        <v>9.4E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="I48" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J48">
         <v>0.05</v>
       </c>
       <c r="K48">
-        <v>3.4889999999999999</v>
-      </c>
-      <c r="L48">
-        <v>1.389</v>
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="L48" t="s">
+        <v>213</v>
       </c>
       <c r="M48" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N48" t="s">
-        <v>210</v>
-      </c>
-      <c r="O48">
-        <v>4.8780000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O48" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+    </row>
+    <row r="49" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D49" t="s">
-        <v>208</v>
+      <c r="D49" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E49">
-        <v>5.8999999999999997E-2</v>
+        <v>4.8780000000000001</v>
       </c>
       <c r="F49">
-        <v>0.17899999999999999</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="G49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H49">
-        <v>0.10199999999999999</v>
+        <v>9.4E-2</v>
       </c>
       <c r="I49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J49">
         <v>0.05</v>
       </c>
-      <c r="K49" t="s">
-        <v>210</v>
+      <c r="K49">
+        <v>3.4889999999999999</v>
       </c>
       <c r="L49">
-        <v>5.8999999999999997E-2</v>
+        <v>1.389</v>
       </c>
       <c r="M49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O49">
-        <v>5.8999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+        <v>4.8780000000000001</v>
+      </c>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+    </row>
+    <row r="50" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
         <v>154</v>
@@ -3397,1080 +3518,1126 @@
       <c r="C50" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D50" t="s">
-        <v>208</v>
+      <c r="D50" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E50">
-        <v>1.2410000000000001</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="F50">
-        <v>0.21199999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="G50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H50">
-        <v>0.121</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J50">
-        <v>0.06</v>
-      </c>
-      <c r="K50">
-        <v>1.0049999999999999</v>
+        <v>0.05</v>
+      </c>
+      <c r="K50" t="s">
+        <v>208</v>
       </c>
       <c r="L50">
-        <v>0.23599999999999999</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="M50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O50">
-        <v>1.2410000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+    </row>
+    <row r="51" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D51" t="s">
-        <v>208</v>
-      </c>
-      <c r="E51" t="s">
-        <v>210</v>
+      <c r="D51" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51">
+        <v>1.2410000000000001</v>
       </c>
       <c r="F51">
-        <v>0.16600000000000001</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="G51" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H51">
-        <v>9.5000000000000001E-2</v>
+        <v>0.121</v>
       </c>
       <c r="I51" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J51">
-        <v>0.05</v>
-      </c>
-      <c r="K51" t="s">
-        <v>210</v>
-      </c>
-      <c r="L51" t="s">
-        <v>210</v>
+        <v>0.06</v>
+      </c>
+      <c r="K51">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="L51">
+        <v>0.23599999999999999</v>
       </c>
       <c r="M51" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N51" t="s">
-        <v>210</v>
-      </c>
-      <c r="O51" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O51">
+        <v>1.2410000000000001</v>
+      </c>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+    </row>
+    <row r="52" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D52" t="s">
-        <v>208</v>
+      <c r="D52" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F52">
-        <v>0.18</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="G52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H52">
-        <v>0.10299999999999999</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J52">
         <v>0.05</v>
       </c>
       <c r="K52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O52" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="9"/>
+    </row>
+    <row r="53" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D53" t="s">
-        <v>208</v>
+      <c r="D53" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F53">
-        <v>0.161</v>
+        <v>0.18</v>
       </c>
       <c r="G53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H53">
-        <v>9.1999999999999998E-2</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="I53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J53">
         <v>0.05</v>
       </c>
       <c r="K53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+    </row>
+    <row r="54" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
-        <v>208</v>
-      </c>
-      <c r="E54">
-        <v>0.97699999999999998</v>
+      <c r="D54" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" t="s">
+        <v>208</v>
       </c>
       <c r="F54">
-        <v>0.17399999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H54">
-        <v>9.9000000000000005E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="I54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J54">
         <v>0.05</v>
       </c>
-      <c r="K54">
-        <v>0.73599999999999999</v>
-      </c>
-      <c r="L54">
-        <v>0.24199999999999999</v>
+      <c r="K54" t="s">
+        <v>208</v>
+      </c>
+      <c r="L54" t="s">
+        <v>208</v>
       </c>
       <c r="M54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N54" t="s">
-        <v>210</v>
-      </c>
-      <c r="O54">
-        <v>0.97699999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O54" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q54" s="9"/>
+      <c r="R54" s="9"/>
+    </row>
+    <row r="55" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D55" t="s">
-        <v>208</v>
+      <c r="D55" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E55">
-        <v>1.2010000000000001</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="F55">
-        <v>0.187</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="G55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H55">
-        <v>0.107</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J55">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K55">
-        <v>1.0229999999999999</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="L55">
-        <v>0.17899999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="M55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O55">
-        <v>1.2010000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+    </row>
+    <row r="56" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D56" t="s">
-        <v>208</v>
+      <c r="D56" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E56">
-        <v>1.1559999999999999</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="F56">
-        <v>0.19500000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="G56" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H56">
-        <v>0.111</v>
+        <v>0.107</v>
       </c>
       <c r="I56" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J56">
         <v>0.06</v>
       </c>
       <c r="K56">
+        <v>1.0229999999999999</v>
+      </c>
+      <c r="L56">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="M56" t="s">
+        <v>208</v>
+      </c>
+      <c r="N56" t="s">
+        <v>208</v>
+      </c>
+      <c r="O56">
+        <v>1.2010000000000001</v>
+      </c>
+      <c r="Q56" s="9"/>
+      <c r="R56" s="9"/>
+    </row>
+    <row r="57" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E57">
+        <v>1.1559999999999999</v>
+      </c>
+      <c r="F57">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="G57" t="s">
+        <v>208</v>
+      </c>
+      <c r="H57">
+        <v>0.111</v>
+      </c>
+      <c r="I57" t="s">
+        <v>208</v>
+      </c>
+      <c r="J57">
+        <v>0.06</v>
+      </c>
+      <c r="K57">
         <v>0.93600000000000005</v>
       </c>
-      <c r="L56">
+      <c r="L57">
         <v>0.22</v>
       </c>
-      <c r="M56" t="s">
-        <v>210</v>
-      </c>
-      <c r="N56" t="s">
-        <v>210</v>
-      </c>
-      <c r="O56">
+      <c r="M57" t="s">
+        <v>208</v>
+      </c>
+      <c r="N57" t="s">
+        <v>208</v>
+      </c>
+      <c r="O57">
         <v>1.1559999999999999</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+    </row>
+    <row r="58" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>70</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>148</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" t="s">
-        <v>208</v>
-      </c>
-      <c r="E57" t="s">
-        <v>210</v>
-      </c>
-      <c r="F57">
-        <v>0.16</v>
-      </c>
-      <c r="G57" t="s">
-        <v>210</v>
-      </c>
-      <c r="H57">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="I57" t="s">
-        <v>210</v>
-      </c>
-      <c r="J57">
-        <v>0.05</v>
-      </c>
-      <c r="K57" t="s">
-        <v>210</v>
-      </c>
-      <c r="L57" t="s">
-        <v>210</v>
-      </c>
-      <c r="M57" t="s">
-        <v>210</v>
-      </c>
-      <c r="N57" t="s">
-        <v>210</v>
-      </c>
-      <c r="O57" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>71</v>
-      </c>
-      <c r="B58" t="s">
-        <v>136</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D58" t="s">
-        <v>208</v>
+      <c r="D58" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F58">
-        <v>0.17699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="G58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H58">
-        <v>0.10100000000000001</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="I58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J58">
         <v>0.05</v>
       </c>
       <c r="K58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O58" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
+    </row>
+    <row r="59" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D59" t="s">
-        <v>208</v>
+      <c r="D59" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F59">
-        <v>0.16400000000000001</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="G59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H59">
-        <v>9.4E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J59">
         <v>0.05</v>
       </c>
       <c r="K59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O59" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q59" s="9"/>
+      <c r="R59" s="9"/>
+    </row>
+    <row r="60" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D60" t="s">
-        <v>208</v>
+      <c r="D60" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F60">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="G60" t="s">
+        <v>208</v>
+      </c>
+      <c r="H60">
+        <v>9.4E-2</v>
+      </c>
+      <c r="I60" t="s">
+        <v>208</v>
+      </c>
+      <c r="J60">
+        <v>0.05</v>
+      </c>
+      <c r="K60" t="s">
+        <v>208</v>
+      </c>
+      <c r="L60" t="s">
+        <v>208</v>
+      </c>
+      <c r="M60" t="s">
+        <v>208</v>
+      </c>
+      <c r="N60" t="s">
+        <v>208</v>
+      </c>
+      <c r="O60" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q60" s="9"/>
+      <c r="R60" s="9"/>
+    </row>
+    <row r="61" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E61" t="s">
+        <v>208</v>
+      </c>
+      <c r="F61">
         <v>0.17799999999999999</v>
       </c>
-      <c r="G60" t="s">
-        <v>210</v>
-      </c>
-      <c r="H60">
+      <c r="G61" t="s">
+        <v>208</v>
+      </c>
+      <c r="H61">
         <v>0.10199999999999999</v>
       </c>
-      <c r="I60" t="s">
-        <v>210</v>
-      </c>
-      <c r="J60">
-        <v>0.05</v>
-      </c>
-      <c r="K60" t="s">
-        <v>210</v>
-      </c>
-      <c r="L60" t="s">
-        <v>210</v>
-      </c>
-      <c r="M60" t="s">
-        <v>210</v>
-      </c>
-      <c r="N60" t="s">
-        <v>210</v>
-      </c>
-      <c r="O60" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="I61" t="s">
+        <v>208</v>
+      </c>
+      <c r="J61">
+        <v>0.05</v>
+      </c>
+      <c r="K61" t="s">
+        <v>208</v>
+      </c>
+      <c r="L61" t="s">
+        <v>208</v>
+      </c>
+      <c r="M61" t="s">
+        <v>208</v>
+      </c>
+      <c r="N61" t="s">
+        <v>208</v>
+      </c>
+      <c r="O61" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+    </row>
+    <row r="62" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>74</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>145</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" t="s">
-        <v>208</v>
-      </c>
-      <c r="E61" t="s">
-        <v>210</v>
-      </c>
-      <c r="F61">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="G61" t="s">
-        <v>210</v>
-      </c>
-      <c r="H61">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="I61" t="s">
-        <v>210</v>
-      </c>
-      <c r="J61">
-        <v>0.05</v>
-      </c>
-      <c r="K61" t="s">
-        <v>210</v>
-      </c>
-      <c r="L61" t="s">
-        <v>210</v>
-      </c>
-      <c r="M61" t="s">
-        <v>210</v>
-      </c>
-      <c r="N61" t="s">
-        <v>210</v>
-      </c>
-      <c r="O61" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B62" t="s">
-        <v>163</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D62" t="s">
-        <v>208</v>
+      <c r="D62" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F62">
-        <v>0.17100000000000001</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H62">
-        <v>9.8000000000000004E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J62">
         <v>0.05</v>
       </c>
       <c r="K62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O62" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+    </row>
+    <row r="63" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D63" t="s">
-        <v>208</v>
+      <c r="D63" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F63">
         <v>0.17100000000000001</v>
       </c>
       <c r="G63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H63">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J63">
         <v>0.05</v>
       </c>
       <c r="K63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O63" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+    </row>
+    <row r="64" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="G64" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="I64" t="s">
+        <v>208</v>
+      </c>
+      <c r="J64">
+        <v>0.05</v>
+      </c>
+      <c r="K64" t="s">
+        <v>208</v>
+      </c>
+      <c r="L64" t="s">
+        <v>208</v>
+      </c>
+      <c r="M64" t="s">
+        <v>208</v>
+      </c>
+      <c r="N64" t="s">
+        <v>208</v>
+      </c>
+      <c r="O64" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q64" s="9"/>
+      <c r="R64" s="9"/>
+    </row>
+    <row r="65" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>77</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D64" t="s">
-        <v>208</v>
-      </c>
-      <c r="E64" t="s">
-        <v>210</v>
-      </c>
-      <c r="F64">
+      <c r="D65" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E65" t="s">
+        <v>208</v>
+      </c>
+      <c r="F65">
         <v>0.161</v>
       </c>
-      <c r="G64" t="s">
-        <v>210</v>
-      </c>
-      <c r="H64">
+      <c r="G65" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="I64" t="s">
-        <v>210</v>
-      </c>
-      <c r="J64">
-        <v>0.05</v>
-      </c>
-      <c r="K64" t="s">
-        <v>210</v>
-      </c>
-      <c r="L64" t="s">
-        <v>210</v>
-      </c>
-      <c r="M64" t="s">
-        <v>210</v>
-      </c>
-      <c r="N64" t="s">
-        <v>210</v>
-      </c>
-      <c r="O64" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="I65" t="s">
+        <v>208</v>
+      </c>
+      <c r="J65">
+        <v>0.05</v>
+      </c>
+      <c r="K65" t="s">
+        <v>208</v>
+      </c>
+      <c r="L65" t="s">
+        <v>208</v>
+      </c>
+      <c r="M65" t="s">
+        <v>208</v>
+      </c>
+      <c r="N65" t="s">
+        <v>208</v>
+      </c>
+      <c r="O65" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q65" s="9"/>
+      <c r="R65" s="9"/>
+    </row>
+    <row r="66" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>78</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D65" t="s">
-        <v>208</v>
-      </c>
-      <c r="E65" t="s">
-        <v>210</v>
-      </c>
-      <c r="F65">
+      <c r="D66" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E66" t="s">
+        <v>208</v>
+      </c>
+      <c r="F66">
         <v>0.17699999999999999</v>
       </c>
-      <c r="G65" t="s">
-        <v>210</v>
-      </c>
-      <c r="H65">
+      <c r="G66" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66">
         <v>0.10100000000000001</v>
       </c>
-      <c r="I65" t="s">
-        <v>210</v>
-      </c>
-      <c r="J65">
-        <v>0.05</v>
-      </c>
-      <c r="K65" t="s">
-        <v>210</v>
-      </c>
-      <c r="L65" t="s">
-        <v>210</v>
-      </c>
-      <c r="M65" t="s">
-        <v>210</v>
-      </c>
-      <c r="N65" t="s">
-        <v>210</v>
-      </c>
-      <c r="O65" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="I66" t="s">
+        <v>208</v>
+      </c>
+      <c r="J66">
+        <v>0.05</v>
+      </c>
+      <c r="K66" t="s">
+        <v>208</v>
+      </c>
+      <c r="L66" t="s">
+        <v>208</v>
+      </c>
+      <c r="M66" t="s">
+        <v>208</v>
+      </c>
+      <c r="N66" t="s">
+        <v>208</v>
+      </c>
+      <c r="O66" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+    </row>
+    <row r="67" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>79</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>140</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" t="s">
-        <v>208</v>
-      </c>
-      <c r="E66" t="s">
-        <v>210</v>
-      </c>
-      <c r="F66">
-        <v>1.335</v>
-      </c>
-      <c r="G66" t="s">
-        <v>210</v>
-      </c>
-      <c r="H66">
-        <v>0.76200000000000001</v>
-      </c>
-      <c r="I66" t="s">
-        <v>210</v>
-      </c>
-      <c r="J66">
-        <v>0.4</v>
-      </c>
-      <c r="K66" t="s">
-        <v>210</v>
-      </c>
-      <c r="L66" t="s">
-        <v>210</v>
-      </c>
-      <c r="M66" t="s">
-        <v>210</v>
-      </c>
-      <c r="N66" t="s">
-        <v>210</v>
-      </c>
-      <c r="O66" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>80</v>
-      </c>
-      <c r="B67" t="s">
-        <v>164</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D67" t="s">
-        <v>208</v>
+      <c r="D67" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E67" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F67">
+        <v>1.335</v>
+      </c>
+      <c r="G67" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="I67" t="s">
+        <v>208</v>
+      </c>
+      <c r="J67">
+        <v>0.4</v>
+      </c>
+      <c r="K67" t="s">
+        <v>208</v>
+      </c>
+      <c r="L67" t="s">
+        <v>208</v>
+      </c>
+      <c r="M67" t="s">
+        <v>208</v>
+      </c>
+      <c r="N67" t="s">
+        <v>208</v>
+      </c>
+      <c r="O67" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+    </row>
+    <row r="68" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E68" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68">
         <v>0.17899999999999999</v>
       </c>
-      <c r="G67" t="s">
-        <v>210</v>
-      </c>
-      <c r="H67">
+      <c r="G68" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68">
         <v>0.10199999999999999</v>
       </c>
-      <c r="I67" t="s">
-        <v>210</v>
-      </c>
-      <c r="J67">
-        <v>0.05</v>
-      </c>
-      <c r="K67" t="s">
-        <v>210</v>
-      </c>
-      <c r="L67" t="s">
-        <v>210</v>
-      </c>
-      <c r="M67" t="s">
-        <v>210</v>
-      </c>
-      <c r="N67" t="s">
-        <v>210</v>
-      </c>
-      <c r="O67" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="I68" t="s">
+        <v>208</v>
+      </c>
+      <c r="J68">
+        <v>0.05</v>
+      </c>
+      <c r="K68" t="s">
+        <v>208</v>
+      </c>
+      <c r="L68" t="s">
+        <v>208</v>
+      </c>
+      <c r="M68" t="s">
+        <v>208</v>
+      </c>
+      <c r="N68" t="s">
+        <v>208</v>
+      </c>
+      <c r="O68" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+    </row>
+    <row r="69" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>81</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>144</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D68" t="s">
-        <v>208</v>
-      </c>
-      <c r="E68" t="s">
-        <v>210</v>
-      </c>
-      <c r="F68">
+      <c r="D69" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E69" t="s">
+        <v>208</v>
+      </c>
+      <c r="F69">
         <v>0.159</v>
       </c>
-      <c r="G68" t="s">
-        <v>210</v>
-      </c>
-      <c r="H68">
+      <c r="G69" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="I68" t="s">
-        <v>210</v>
-      </c>
-      <c r="J68">
-        <v>0.05</v>
-      </c>
-      <c r="K68" t="s">
-        <v>210</v>
-      </c>
-      <c r="L68" t="s">
-        <v>210</v>
-      </c>
-      <c r="M68" t="s">
-        <v>210</v>
-      </c>
-      <c r="N68" t="s">
-        <v>210</v>
-      </c>
-      <c r="O68" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="I69" t="s">
+        <v>208</v>
+      </c>
+      <c r="J69">
+        <v>0.05</v>
+      </c>
+      <c r="K69" t="s">
+        <v>208</v>
+      </c>
+      <c r="L69" t="s">
+        <v>208</v>
+      </c>
+      <c r="M69" t="s">
+        <v>208</v>
+      </c>
+      <c r="N69" t="s">
+        <v>208</v>
+      </c>
+      <c r="O69" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+    </row>
+    <row r="70" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>82</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>147</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
-      </c>
-      <c r="E69" t="s">
-        <v>210</v>
-      </c>
-      <c r="F69">
-        <v>0.33400000000000002</v>
-      </c>
-      <c r="G69" t="s">
-        <v>210</v>
-      </c>
-      <c r="H69">
-        <v>0.191</v>
-      </c>
-      <c r="I69" t="s">
-        <v>210</v>
-      </c>
-      <c r="J69">
-        <v>0.1</v>
-      </c>
-      <c r="K69" t="s">
-        <v>210</v>
-      </c>
-      <c r="L69" t="s">
-        <v>210</v>
-      </c>
-      <c r="M69" t="s">
-        <v>210</v>
-      </c>
-      <c r="N69" t="s">
-        <v>210</v>
-      </c>
-      <c r="O69" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>83</v>
-      </c>
-      <c r="B70" t="s">
-        <v>145</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D70" t="s">
-        <v>208</v>
+      <c r="D70" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E70" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F70">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="G70" t="s">
+        <v>208</v>
+      </c>
+      <c r="H70">
+        <v>0.191</v>
+      </c>
+      <c r="I70" t="s">
+        <v>208</v>
+      </c>
+      <c r="J70">
+        <v>0.1</v>
+      </c>
+      <c r="K70" t="s">
+        <v>208</v>
+      </c>
+      <c r="L70" t="s">
+        <v>208</v>
+      </c>
+      <c r="M70" t="s">
+        <v>208</v>
+      </c>
+      <c r="N70" t="s">
+        <v>208</v>
+      </c>
+      <c r="O70" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q70" s="9"/>
+      <c r="R70" s="9"/>
+    </row>
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E71" t="s">
+        <v>208</v>
+      </c>
+      <c r="F71">
         <v>0.16800000000000001</v>
       </c>
-      <c r="G70" t="s">
-        <v>210</v>
-      </c>
-      <c r="H70">
+      <c r="G71" t="s">
+        <v>208</v>
+      </c>
+      <c r="H71">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="I70" t="s">
-        <v>210</v>
-      </c>
-      <c r="J70">
-        <v>0.05</v>
-      </c>
-      <c r="K70" t="s">
-        <v>210</v>
-      </c>
-      <c r="L70" t="s">
-        <v>210</v>
-      </c>
-      <c r="M70" t="s">
-        <v>210</v>
-      </c>
-      <c r="N70" t="s">
-        <v>210</v>
-      </c>
-      <c r="O70" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="I71" t="s">
+        <v>208</v>
+      </c>
+      <c r="J71">
+        <v>0.05</v>
+      </c>
+      <c r="K71" t="s">
+        <v>208</v>
+      </c>
+      <c r="L71" t="s">
+        <v>208</v>
+      </c>
+      <c r="M71" t="s">
+        <v>208</v>
+      </c>
+      <c r="N71" t="s">
+        <v>208</v>
+      </c>
+      <c r="O71" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
+    </row>
+    <row r="72" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>84</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>165</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D71" t="s">
-        <v>209</v>
-      </c>
-      <c r="E71" t="s">
-        <v>210</v>
-      </c>
-      <c r="F71">
+      <c r="D72" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E72" t="s">
+        <v>208</v>
+      </c>
+      <c r="F72">
         <v>3.39</v>
       </c>
-      <c r="G71" t="s">
-        <v>210</v>
-      </c>
-      <c r="H71">
+      <c r="G72" t="s">
+        <v>208</v>
+      </c>
+      <c r="H72">
         <v>1.9370000000000001</v>
       </c>
-      <c r="I71" t="s">
-        <v>210</v>
-      </c>
-      <c r="J71">
+      <c r="I72" t="s">
+        <v>208</v>
+      </c>
+      <c r="J72">
         <v>1.01</v>
       </c>
-      <c r="K71" t="s">
-        <v>210</v>
-      </c>
-      <c r="L71" t="s">
-        <v>210</v>
-      </c>
-      <c r="M71" t="s">
-        <v>210</v>
-      </c>
-      <c r="N71" t="s">
-        <v>210</v>
-      </c>
-      <c r="O71" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="K72" t="s">
+        <v>208</v>
+      </c>
+      <c r="L72" t="s">
+        <v>208</v>
+      </c>
+      <c r="M72" t="s">
+        <v>208</v>
+      </c>
+      <c r="N72" t="s">
+        <v>208</v>
+      </c>
+      <c r="O72" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q72" s="9"/>
+      <c r="R72" s="9"/>
+    </row>
+    <row r="73" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>85</v>
-      </c>
-      <c r="B72" t="s">
-        <v>149</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D72" t="s">
-        <v>208</v>
-      </c>
-      <c r="E72">
-        <v>2.0510000000000002</v>
-      </c>
-      <c r="F72">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="G72" t="s">
-        <v>210</v>
-      </c>
-      <c r="H72">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="I72" t="s">
-        <v>210</v>
-      </c>
-      <c r="J72">
-        <v>0.05</v>
-      </c>
-      <c r="K72">
-        <v>1.4359999999999999</v>
-      </c>
-      <c r="L72">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="M72" t="s">
-        <v>210</v>
-      </c>
-      <c r="N72" t="s">
-        <v>210</v>
-      </c>
-      <c r="O72">
-        <v>2.0510000000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>86</v>
       </c>
       <c r="B73" t="s">
         <v>149</v>
@@ -4478,93 +4645,97 @@
       <c r="C73" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D73" t="s">
-        <v>208</v>
+      <c r="D73" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E73">
-        <v>2.0830000000000002</v>
+        <v>2.0510000000000002</v>
       </c>
       <c r="F73">
-        <v>0.17</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="G73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H73">
-        <v>9.7000000000000003E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J73">
         <v>0.05</v>
       </c>
       <c r="K73">
-        <v>1.5289999999999999</v>
+        <v>1.4359999999999999</v>
       </c>
       <c r="L73">
-        <v>0.55300000000000005</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="M73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O73">
-        <v>2.0830000000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+        <v>2.0510000000000002</v>
+      </c>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+    </row>
+    <row r="74" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D74" t="s">
-        <v>208</v>
+      <c r="D74" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E74">
-        <v>0.34100000000000003</v>
+        <v>2.0830000000000002</v>
       </c>
       <c r="F74">
-        <v>0.159</v>
+        <v>0.17</v>
       </c>
       <c r="G74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H74">
-        <v>9.0999999999999998E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J74">
         <v>0.05</v>
       </c>
       <c r="K74">
-        <v>0.26200000000000001</v>
+        <v>1.5289999999999999</v>
       </c>
       <c r="L74">
-        <v>7.8E-2</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="M74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O74">
-        <v>0.34100000000000003</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+        <v>2.0830000000000002</v>
+      </c>
+      <c r="Q74" s="9"/>
+      <c r="R74" s="9"/>
+    </row>
+    <row r="75" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B75" t="s">
         <v>150</v>
@@ -4572,281 +4743,293 @@
       <c r="C75" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D75" t="s">
-        <v>208</v>
+      <c r="D75" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E75">
-        <v>2.242</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F75">
-        <v>0.20799999999999999</v>
+        <v>0.159</v>
       </c>
       <c r="G75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H75">
-        <v>0.11899999999999999</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="I75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J75">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K75">
-        <v>1.4239999999999999</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="L75">
-        <v>0.81799999999999995</v>
+        <v>7.8E-2</v>
       </c>
       <c r="M75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O75">
-        <v>2.242</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+    </row>
+    <row r="76" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D76" t="s">
-        <v>208</v>
+      <c r="D76" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E76">
-        <v>1.6970000000000001</v>
+        <v>2.242</v>
       </c>
       <c r="F76">
-        <v>0.17899999999999999</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="G76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H76">
-        <v>0.10199999999999999</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J76">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K76">
-        <v>1.23</v>
+        <v>1.4239999999999999</v>
       </c>
       <c r="L76">
-        <v>0.46600000000000003</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="M76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O76">
-        <v>1.6970000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+        <v>2.242</v>
+      </c>
+      <c r="Q76" s="9"/>
+      <c r="R76" s="9"/>
+    </row>
+    <row r="77" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D77" t="s">
-        <v>208</v>
+      <c r="D77" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E77">
-        <v>6.7</v>
+        <v>1.6970000000000001</v>
       </c>
       <c r="F77">
-        <v>0.20699999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="G77" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H77">
-        <v>0.11899999999999999</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="I77" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J77">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K77">
-        <v>4.9550000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="L77">
-        <v>1.744</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="M77" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N77" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O77">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+        <v>1.6970000000000001</v>
+      </c>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+    </row>
+    <row r="78" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D78" t="s">
-        <v>208</v>
+      <c r="D78" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E78">
-        <v>6.4569999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="F78">
-        <v>0.17799999999999999</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H78">
-        <v>0.10100000000000001</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J78">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K78">
-        <v>4.6890000000000001</v>
+        <v>4.9550000000000001</v>
       </c>
       <c r="L78">
-        <v>1.768</v>
+        <v>1.744</v>
       </c>
       <c r="M78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O78">
-        <v>6.4569999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+        <v>6.7</v>
+      </c>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9"/>
+    </row>
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D79" t="s">
-        <v>208</v>
+      <c r="D79" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E79">
-        <v>6.577</v>
+        <v>6.4569999999999999</v>
       </c>
       <c r="F79">
-        <v>0.19</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="G79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H79">
-        <v>0.109</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J79">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K79">
-        <v>4.5510000000000002</v>
+        <v>4.6890000000000001</v>
       </c>
       <c r="L79">
-        <v>2.0259999999999998</v>
+        <v>1.768</v>
       </c>
       <c r="M79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O79">
-        <v>6.577</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+        <v>6.4569999999999999</v>
+      </c>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
+    </row>
+    <row r="80" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D80" t="s">
-        <v>208</v>
+      <c r="D80" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E80">
-        <v>1.0669999999999999</v>
+        <v>6.577</v>
       </c>
       <c r="F80">
-        <v>0.182</v>
+        <v>0.19</v>
       </c>
       <c r="G80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H80">
-        <v>0.104</v>
+        <v>0.109</v>
       </c>
       <c r="I80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J80">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K80">
-        <v>0.66300000000000003</v>
+        <v>4.5510000000000002</v>
       </c>
       <c r="L80">
-        <v>0.40400000000000003</v>
+        <v>2.0259999999999998</v>
       </c>
       <c r="M80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O80">
-        <v>1.0669999999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+        <v>6.577</v>
+      </c>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="9"/>
+    </row>
+    <row r="81" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
         <v>155</v>
@@ -4854,984 +5037,1026 @@
       <c r="C81" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D81" t="s">
-        <v>208</v>
+      <c r="D81" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E81">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="F81">
+        <v>0.182</v>
+      </c>
+      <c r="G81" t="s">
+        <v>208</v>
+      </c>
+      <c r="H81">
+        <v>0.104</v>
+      </c>
+      <c r="I81" t="s">
+        <v>208</v>
+      </c>
+      <c r="J81">
+        <v>0.05</v>
+      </c>
+      <c r="K81">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="L81">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="M81" t="s">
+        <v>208</v>
+      </c>
+      <c r="N81" t="s">
+        <v>208</v>
+      </c>
+      <c r="O81">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="Q81" s="9"/>
+      <c r="R81" s="9"/>
+    </row>
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E82">
         <v>1.1719999999999999</v>
       </c>
-      <c r="F81">
+      <c r="F82">
         <v>0.17</v>
       </c>
-      <c r="G81" t="s">
-        <v>210</v>
-      </c>
-      <c r="H81">
+      <c r="G82" t="s">
+        <v>208</v>
+      </c>
+      <c r="H82">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="I81" t="s">
-        <v>210</v>
-      </c>
-      <c r="J81">
-        <v>0.05</v>
-      </c>
-      <c r="K81">
+      <c r="I82" t="s">
+        <v>208</v>
+      </c>
+      <c r="J82">
+        <v>0.05</v>
+      </c>
+      <c r="K82">
         <v>0.746</v>
       </c>
-      <c r="L81">
+      <c r="L82">
         <v>0.42599999999999999</v>
       </c>
-      <c r="M81" t="s">
-        <v>210</v>
-      </c>
-      <c r="N81" t="s">
-        <v>210</v>
-      </c>
-      <c r="O81">
+      <c r="M82" t="s">
+        <v>208</v>
+      </c>
+      <c r="N82" t="s">
+        <v>208</v>
+      </c>
+      <c r="O82">
         <v>1.1719999999999999</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="Q82" s="9"/>
+      <c r="R82" s="9"/>
+    </row>
+    <row r="83" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>95</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>139</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D82" t="s">
-        <v>208</v>
-      </c>
-      <c r="E82" t="s">
-        <v>210</v>
-      </c>
-      <c r="F82">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="G82" t="s">
-        <v>210</v>
-      </c>
-      <c r="H82">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="I82" t="s">
-        <v>210</v>
-      </c>
-      <c r="J82">
-        <v>0.05</v>
-      </c>
-      <c r="K82" t="s">
-        <v>210</v>
-      </c>
-      <c r="L82" t="s">
-        <v>210</v>
-      </c>
-      <c r="M82" t="s">
-        <v>210</v>
-      </c>
-      <c r="N82" t="s">
-        <v>210</v>
-      </c>
-      <c r="O82" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>96</v>
-      </c>
-      <c r="B83" t="s">
-        <v>138</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D83" t="s">
-        <v>208</v>
+      <c r="D83" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F83">
-        <v>0.17699999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="G83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H83">
-        <v>0.10100000000000001</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J83">
         <v>0.05</v>
       </c>
       <c r="K83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N83" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O83" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q83" s="9"/>
+      <c r="R83" s="9"/>
+    </row>
+    <row r="84" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D84" t="s">
-        <v>208</v>
+      <c r="D84" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E84" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F84">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="G84" t="s">
+        <v>208</v>
+      </c>
+      <c r="H84">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I84" t="s">
+        <v>208</v>
+      </c>
+      <c r="J84">
+        <v>0.05</v>
+      </c>
+      <c r="K84" t="s">
+        <v>208</v>
+      </c>
+      <c r="L84" t="s">
+        <v>208</v>
+      </c>
+      <c r="M84" t="s">
+        <v>208</v>
+      </c>
+      <c r="N84" t="s">
+        <v>208</v>
+      </c>
+      <c r="O84" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q84" s="9"/>
+      <c r="R84" s="9"/>
+    </row>
+    <row r="85" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>97</v>
+      </c>
+      <c r="B85" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E85" t="s">
+        <v>208</v>
+      </c>
+      <c r="F85">
         <v>0.16</v>
       </c>
-      <c r="G84" t="s">
-        <v>210</v>
-      </c>
-      <c r="H84">
+      <c r="G85" t="s">
+        <v>208</v>
+      </c>
+      <c r="H85">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="I84" t="s">
-        <v>210</v>
-      </c>
-      <c r="J84">
-        <v>0.05</v>
-      </c>
-      <c r="K84" t="s">
-        <v>210</v>
-      </c>
-      <c r="L84" t="s">
-        <v>210</v>
-      </c>
-      <c r="M84" t="s">
-        <v>210</v>
-      </c>
-      <c r="N84" t="s">
-        <v>210</v>
-      </c>
-      <c r="O84" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="I85" t="s">
+        <v>208</v>
+      </c>
+      <c r="J85">
+        <v>0.05</v>
+      </c>
+      <c r="K85" t="s">
+        <v>208</v>
+      </c>
+      <c r="L85" t="s">
+        <v>208</v>
+      </c>
+      <c r="M85" t="s">
+        <v>208</v>
+      </c>
+      <c r="N85" t="s">
+        <v>208</v>
+      </c>
+      <c r="O85" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+    </row>
+    <row r="86" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>98</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>143</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D85" t="s">
-        <v>208</v>
-      </c>
-      <c r="E85" t="s">
-        <v>210</v>
-      </c>
-      <c r="F85">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="G85" t="s">
-        <v>210</v>
-      </c>
-      <c r="H85">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="I85" t="s">
-        <v>210</v>
-      </c>
-      <c r="J85">
-        <v>0.05</v>
-      </c>
-      <c r="K85" t="s">
-        <v>210</v>
-      </c>
-      <c r="L85" t="s">
-        <v>210</v>
-      </c>
-      <c r="M85" t="s">
-        <v>210</v>
-      </c>
-      <c r="N85" t="s">
-        <v>210</v>
-      </c>
-      <c r="O85" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>99</v>
-      </c>
-      <c r="B86" t="s">
-        <v>145</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D86" t="s">
-        <v>208</v>
+      <c r="D86" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E86" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F86">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="G86" t="s">
+        <v>208</v>
+      </c>
+      <c r="H86">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="I86" t="s">
+        <v>208</v>
+      </c>
+      <c r="J86">
+        <v>0.05</v>
+      </c>
+      <c r="K86" t="s">
+        <v>208</v>
+      </c>
+      <c r="L86" t="s">
+        <v>208</v>
+      </c>
+      <c r="M86" t="s">
+        <v>208</v>
+      </c>
+      <c r="N86" t="s">
+        <v>208</v>
+      </c>
+      <c r="O86" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q86" s="9"/>
+      <c r="R86" s="9"/>
+    </row>
+    <row r="87" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87" t="s">
+        <v>145</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E87" t="s">
+        <v>208</v>
+      </c>
+      <c r="F87">
         <v>0.16600000000000001</v>
       </c>
-      <c r="G86" t="s">
-        <v>210</v>
-      </c>
-      <c r="H86">
+      <c r="G87" t="s">
+        <v>208</v>
+      </c>
+      <c r="H87">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="I86" t="s">
-        <v>210</v>
-      </c>
-      <c r="J86">
-        <v>0.05</v>
-      </c>
-      <c r="K86" t="s">
-        <v>210</v>
-      </c>
-      <c r="L86" t="s">
-        <v>210</v>
-      </c>
-      <c r="M86" t="s">
-        <v>210</v>
-      </c>
-      <c r="N86" t="s">
-        <v>210</v>
-      </c>
-      <c r="O86" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="I87" t="s">
+        <v>208</v>
+      </c>
+      <c r="J87">
+        <v>0.05</v>
+      </c>
+      <c r="K87" t="s">
+        <v>208</v>
+      </c>
+      <c r="L87" t="s">
+        <v>208</v>
+      </c>
+      <c r="M87" t="s">
+        <v>208</v>
+      </c>
+      <c r="N87" t="s">
+        <v>208</v>
+      </c>
+      <c r="O87" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="9"/>
+    </row>
+    <row r="88" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>100</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>148</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D87" t="s">
-        <v>208</v>
-      </c>
-      <c r="E87" t="s">
-        <v>210</v>
-      </c>
-      <c r="F87">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="G87" t="s">
-        <v>210</v>
-      </c>
-      <c r="H87">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="I87" t="s">
-        <v>210</v>
-      </c>
-      <c r="J87">
-        <v>0.05</v>
-      </c>
-      <c r="K87" t="s">
-        <v>210</v>
-      </c>
-      <c r="L87" t="s">
-        <v>210</v>
-      </c>
-      <c r="M87" t="s">
-        <v>210</v>
-      </c>
-      <c r="N87" t="s">
-        <v>210</v>
-      </c>
-      <c r="O87" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>101</v>
-      </c>
-      <c r="B88" t="s">
-        <v>141</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D88" t="s">
-        <v>208</v>
-      </c>
-      <c r="E88">
+      <c r="D88" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E88" t="s">
+        <v>208</v>
+      </c>
+      <c r="F88">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="G88" t="s">
+        <v>208</v>
+      </c>
+      <c r="H88">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I88" t="s">
+        <v>208</v>
+      </c>
+      <c r="J88">
+        <v>0.05</v>
+      </c>
+      <c r="K88" t="s">
+        <v>208</v>
+      </c>
+      <c r="L88" t="s">
+        <v>208</v>
+      </c>
+      <c r="M88" t="s">
+        <v>208</v>
+      </c>
+      <c r="N88" t="s">
+        <v>208</v>
+      </c>
+      <c r="O88" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q88" s="9"/>
+      <c r="R88" s="9"/>
+    </row>
+    <row r="89" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E89">
         <v>0.55700000000000005</v>
       </c>
-      <c r="F88">
+      <c r="F89">
         <v>0.16700000000000001</v>
       </c>
-      <c r="G88" t="s">
-        <v>210</v>
-      </c>
-      <c r="H88">
+      <c r="G89" t="s">
+        <v>208</v>
+      </c>
+      <c r="H89">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="I88" t="s">
-        <v>210</v>
-      </c>
-      <c r="J88">
-        <v>0.05</v>
-      </c>
-      <c r="K88" t="s">
-        <v>210</v>
-      </c>
-      <c r="L88">
+      <c r="I89" t="s">
+        <v>208</v>
+      </c>
+      <c r="J89">
+        <v>0.05</v>
+      </c>
+      <c r="K89" t="s">
+        <v>208</v>
+      </c>
+      <c r="L89">
         <v>0.55700000000000005</v>
       </c>
-      <c r="M88" t="s">
-        <v>210</v>
-      </c>
-      <c r="N88" t="s">
-        <v>210</v>
-      </c>
-      <c r="O88">
+      <c r="M89" t="s">
+        <v>208</v>
+      </c>
+      <c r="N89" t="s">
+        <v>208</v>
+      </c>
+      <c r="O89">
         <v>0.55700000000000005</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+    </row>
+    <row r="90" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>102</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>149</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D89" t="s">
-        <v>208</v>
-      </c>
-      <c r="E89" t="s">
-        <v>210</v>
-      </c>
-      <c r="F89">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="G89" t="s">
-        <v>210</v>
-      </c>
-      <c r="H89">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="I89" t="s">
-        <v>210</v>
-      </c>
-      <c r="J89">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K89" t="s">
-        <v>210</v>
-      </c>
-      <c r="L89" t="s">
-        <v>210</v>
-      </c>
-      <c r="M89" t="s">
-        <v>210</v>
-      </c>
-      <c r="N89" t="s">
-        <v>210</v>
-      </c>
-      <c r="O89" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>103</v>
-      </c>
-      <c r="B90" t="s">
-        <v>150</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D90" t="s">
-        <v>208</v>
+      <c r="D90" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F90">
-        <v>0.16600000000000001</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="G90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H90">
-        <v>9.5000000000000001E-2</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="I90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J90">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O90" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q90" s="9"/>
+      <c r="R90" s="9"/>
+    </row>
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D91" t="s">
-        <v>208</v>
+      <c r="D91" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F91">
-        <v>0.16200000000000001</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="G91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H91">
-        <v>9.1999999999999998E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J91">
         <v>0.05</v>
       </c>
       <c r="K91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O91" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+    </row>
+    <row r="92" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D92" t="s">
-        <v>208</v>
+      <c r="D92" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F92">
-        <v>0.17199999999999999</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H92">
-        <v>9.8000000000000004E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="I92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J92">
         <v>0.05</v>
       </c>
       <c r="K92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O92" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q92" s="9"/>
+      <c r="R92" s="9"/>
+    </row>
+    <row r="93" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D93" t="s">
-        <v>208</v>
+      <c r="D93" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F93">
-        <v>0.18099999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="G93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H93">
-        <v>0.10299999999999999</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J93">
         <v>0.05</v>
       </c>
       <c r="K93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O93" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+    </row>
+    <row r="94" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D94" t="s">
-        <v>208</v>
+      <c r="D94" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E94" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F94">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="G94" t="s">
+        <v>208</v>
+      </c>
+      <c r="H94">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I94" t="s">
+        <v>208</v>
+      </c>
+      <c r="J94">
+        <v>0.05</v>
+      </c>
+      <c r="K94" t="s">
+        <v>208</v>
+      </c>
+      <c r="L94" t="s">
+        <v>208</v>
+      </c>
+      <c r="M94" t="s">
+        <v>208</v>
+      </c>
+      <c r="N94" t="s">
+        <v>208</v>
+      </c>
+      <c r="O94" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q94" s="9"/>
+      <c r="R94" s="9"/>
+    </row>
+    <row r="95" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>107</v>
+      </c>
+      <c r="B95" t="s">
+        <v>155</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E95" t="s">
+        <v>208</v>
+      </c>
+      <c r="F95">
         <v>0.17499999999999999</v>
       </c>
-      <c r="G94" t="s">
-        <v>210</v>
-      </c>
-      <c r="H94">
+      <c r="G95" t="s">
+        <v>208</v>
+      </c>
+      <c r="H95">
         <v>0.1</v>
       </c>
-      <c r="I94" t="s">
-        <v>210</v>
-      </c>
-      <c r="J94">
-        <v>0.05</v>
-      </c>
-      <c r="K94" t="s">
-        <v>210</v>
-      </c>
-      <c r="L94" t="s">
-        <v>210</v>
-      </c>
-      <c r="M94" t="s">
-        <v>210</v>
-      </c>
-      <c r="N94" t="s">
-        <v>210</v>
-      </c>
-      <c r="O94" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="I95" t="s">
+        <v>208</v>
+      </c>
+      <c r="J95">
+        <v>0.05</v>
+      </c>
+      <c r="K95" t="s">
+        <v>208</v>
+      </c>
+      <c r="L95" t="s">
+        <v>208</v>
+      </c>
+      <c r="M95" t="s">
+        <v>208</v>
+      </c>
+      <c r="N95" t="s">
+        <v>208</v>
+      </c>
+      <c r="O95" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+    </row>
+    <row r="96" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>108</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>149</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D95" t="s">
-        <v>208</v>
-      </c>
-      <c r="E95" t="s">
-        <v>210</v>
-      </c>
-      <c r="F95">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="G95" t="s">
-        <v>210</v>
-      </c>
-      <c r="H95">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="I95" t="s">
-        <v>210</v>
-      </c>
-      <c r="J95">
-        <v>0.05</v>
-      </c>
-      <c r="K95" t="s">
-        <v>210</v>
-      </c>
-      <c r="L95" t="s">
-        <v>210</v>
-      </c>
-      <c r="M95" t="s">
-        <v>210</v>
-      </c>
-      <c r="N95" t="s">
-        <v>210</v>
-      </c>
-      <c r="O95" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>109</v>
-      </c>
-      <c r="B96" t="s">
-        <v>156</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D96" t="s">
-        <v>208</v>
-      </c>
-      <c r="E96">
-        <v>7.0999999999999994E-2</v>
+      <c r="D96" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E96" t="s">
+        <v>208</v>
       </c>
       <c r="F96">
-        <v>0.18</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="G96" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H96">
-        <v>0.10299999999999999</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I96" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J96">
         <v>0.05</v>
       </c>
       <c r="K96" t="s">
-        <v>210</v>
-      </c>
-      <c r="L96">
-        <v>7.0999999999999994E-2</v>
+        <v>208</v>
+      </c>
+      <c r="L96" t="s">
+        <v>208</v>
       </c>
       <c r="M96" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N96" t="s">
-        <v>210</v>
-      </c>
-      <c r="O96">
-        <v>7.0999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O96" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q96" s="9"/>
+      <c r="R96" s="9"/>
+    </row>
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D97" t="s">
-        <v>208</v>
+      <c r="D97" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E97">
-        <v>8.7999999999999995E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="F97">
-        <v>0.157</v>
+        <v>0.18</v>
       </c>
       <c r="G97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H97">
-        <v>0.09</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="I97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J97">
         <v>0.05</v>
       </c>
       <c r="K97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L97">
-        <v>8.7999999999999995E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="M97" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N97" t="s">
-        <v>210</v>
-      </c>
-      <c r="O97" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="O97">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+    </row>
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D98" t="s">
-        <v>208</v>
-      </c>
-      <c r="E98" t="s">
-        <v>210</v>
+      <c r="D98" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E98">
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="F98">
-        <v>0.183</v>
+        <v>0.157</v>
       </c>
       <c r="G98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H98">
-        <v>0.104</v>
+        <v>0.09</v>
       </c>
       <c r="I98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J98">
         <v>0.05</v>
       </c>
       <c r="K98" t="s">
-        <v>210</v>
-      </c>
-      <c r="L98" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="L98">
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="M98" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O98" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
+    </row>
+    <row r="99" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B99" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D99" t="s">
-        <v>208</v>
+      <c r="D99" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F99">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="G99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H99">
-        <v>0.10299999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="I99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J99">
         <v>0.05</v>
       </c>
       <c r="K99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O99" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q99" s="9"/>
+      <c r="R99" s="9"/>
+    </row>
+    <row r="100" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D100" t="s">
-        <v>208</v>
+      <c r="D100" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E100" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F100">
+        <v>0.18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>208</v>
+      </c>
+      <c r="H100">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I100" t="s">
+        <v>208</v>
+      </c>
+      <c r="J100">
+        <v>0.05</v>
+      </c>
+      <c r="K100" t="s">
+        <v>208</v>
+      </c>
+      <c r="L100" t="s">
+        <v>208</v>
+      </c>
+      <c r="M100" t="s">
+        <v>208</v>
+      </c>
+      <c r="N100" t="s">
+        <v>208</v>
+      </c>
+      <c r="O100" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q100" s="9"/>
+      <c r="R100" s="9"/>
+    </row>
+    <row r="101" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" t="s">
+        <v>155</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E101" t="s">
+        <v>208</v>
+      </c>
+      <c r="F101">
         <v>0.159</v>
       </c>
-      <c r="G100" t="s">
-        <v>210</v>
-      </c>
-      <c r="H100">
+      <c r="G101" t="s">
+        <v>208</v>
+      </c>
+      <c r="H101">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="I100" t="s">
-        <v>210</v>
-      </c>
-      <c r="J100">
-        <v>0.05</v>
-      </c>
-      <c r="K100" t="s">
-        <v>210</v>
-      </c>
-      <c r="L100" t="s">
-        <v>210</v>
-      </c>
-      <c r="M100" t="s">
-        <v>210</v>
-      </c>
-      <c r="N100" t="s">
-        <v>210</v>
-      </c>
-      <c r="O100" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>114</v>
-      </c>
-      <c r="B101" t="s">
-        <v>149</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D101" t="s">
-        <v>208</v>
-      </c>
-      <c r="E101" t="s">
-        <v>210</v>
-      </c>
-      <c r="F101">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G101" t="s">
-        <v>210</v>
-      </c>
-      <c r="H101">
-        <v>0.1</v>
-      </c>
       <c r="I101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J101">
         <v>0.05</v>
       </c>
       <c r="K101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O101" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
+    </row>
+    <row r="102" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -5841,44 +6066,46 @@
       <c r="C102" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
-        <v>208</v>
+      <c r="D102" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F102">
         <v>0.29899999999999999</v>
       </c>
       <c r="G102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H102">
         <v>0.17100000000000001</v>
       </c>
       <c r="I102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J102">
         <v>0.09</v>
       </c>
       <c r="K102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O102" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q102" s="9"/>
+      <c r="R102" s="9"/>
+    </row>
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -5888,8 +6115,8 @@
       <c r="C103" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
-        <v>208</v>
+      <c r="D103" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E103">
         <v>12.085000000000001</v>
@@ -5898,13 +6125,13 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G103" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H103">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="I103" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J103">
         <v>0.05</v>
@@ -5924,8 +6151,10 @@
       <c r="O103">
         <v>12.085000000000001</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+    </row>
+    <row r="104" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -5935,8 +6164,8 @@
       <c r="C104" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D104" t="s">
-        <v>208</v>
+      <c r="D104" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E104">
         <v>0.59199999999999997</v>
@@ -5945,34 +6174,36 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="G104" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H104">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I104" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J104">
         <v>0.05</v>
       </c>
       <c r="K104" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L104">
         <v>0.59199999999999997</v>
       </c>
       <c r="M104" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N104" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O104">
         <v>0.59199999999999997</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q104" s="9"/>
+      <c r="R104" s="9"/>
+    </row>
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -5982,44 +6213,46 @@
       <c r="C105" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D105" t="s">
-        <v>208</v>
+      <c r="D105" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F105">
         <v>0.28299999999999997</v>
       </c>
       <c r="G105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H105">
         <v>0.16200000000000001</v>
       </c>
       <c r="I105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J105">
         <v>0.08</v>
       </c>
       <c r="K105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O105" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q105" s="9"/>
+      <c r="R105" s="9"/>
+    </row>
+    <row r="106" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -6029,8 +6262,8 @@
       <c r="C106" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D106" t="s">
-        <v>208</v>
+      <c r="D106" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E106">
         <v>0.215</v>
@@ -6039,34 +6272,36 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="G106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H106">
         <v>0.1</v>
       </c>
       <c r="I106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J106">
         <v>0.05</v>
       </c>
       <c r="K106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L106">
         <v>0.215</v>
       </c>
       <c r="M106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O106">
         <v>0.215</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q106" s="9"/>
+      <c r="R106" s="9"/>
+    </row>
+    <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -6076,44 +6311,46 @@
       <c r="C107" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D107" t="s">
-        <v>208</v>
+      <c r="D107" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F107">
         <v>0.17299999999999999</v>
       </c>
       <c r="G107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H107">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="I107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J107">
         <v>0.05</v>
       </c>
       <c r="K107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O107" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+    </row>
+    <row r="108" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -6123,44 +6360,46 @@
       <c r="C108" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D108" t="s">
-        <v>208</v>
+      <c r="D108" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F108">
         <v>0.16300000000000001</v>
       </c>
       <c r="G108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H108">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J108">
         <v>0.05</v>
       </c>
       <c r="K108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O108" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q108" s="9"/>
+      <c r="R108" s="9"/>
+    </row>
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>122</v>
       </c>
@@ -6170,44 +6409,46 @@
       <c r="C109" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D109" t="s">
-        <v>208</v>
+      <c r="D109" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F109">
         <v>0.16300000000000001</v>
       </c>
       <c r="G109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H109">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="I109" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J109">
         <v>0.05</v>
       </c>
       <c r="K109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N109" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O109" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+    </row>
+    <row r="110" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -6217,44 +6458,46 @@
       <c r="C110" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D110" t="s">
-        <v>208</v>
+      <c r="D110" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F110">
         <v>0.17199999999999999</v>
       </c>
       <c r="G110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H110">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="I110" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J110">
         <v>0.05</v>
       </c>
       <c r="K110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O110" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q110" s="9"/>
+      <c r="R110" s="9"/>
+    </row>
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -6264,44 +6507,46 @@
       <c r="C111" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D111" t="s">
-        <v>208</v>
+      <c r="D111" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F111">
         <v>0.189</v>
       </c>
       <c r="G111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H111">
         <v>0.108</v>
       </c>
       <c r="I111" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J111">
         <v>0.06</v>
       </c>
       <c r="K111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N111" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O111" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+    </row>
+    <row r="112" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -6311,44 +6556,46 @@
       <c r="C112" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D112" t="s">
-        <v>208</v>
+      <c r="D112" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F112">
         <v>0.156</v>
       </c>
       <c r="G112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H112">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="I112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J112">
         <v>0.05</v>
       </c>
       <c r="K112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N112" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O112" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q112" s="9"/>
+      <c r="R112" s="9"/>
+    </row>
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -6358,44 +6605,46 @@
       <c r="C113" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D113" t="s">
-        <v>208</v>
+      <c r="D113" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F113">
         <v>4.5810000000000004</v>
       </c>
       <c r="G113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H113">
         <v>2.617</v>
       </c>
       <c r="I113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J113">
         <v>1.37</v>
       </c>
       <c r="K113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N113" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O113" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+    </row>
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -6405,44 +6654,46 @@
       <c r="C114" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D114" t="s">
-        <v>208</v>
+      <c r="D114" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="E114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F114">
         <v>2.4929999999999999</v>
       </c>
       <c r="G114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H114">
         <v>1.4239999999999999</v>
       </c>
       <c r="I114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J114">
         <v>0.74</v>
       </c>
       <c r="K114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O114" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="9"/>
+    </row>
+    <row r="115" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -6453,43 +6704,44 @@
         <v>186</v>
       </c>
       <c r="D115" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F115">
         <v>3.39</v>
       </c>
       <c r="G115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H115">
         <v>1.9370000000000001</v>
       </c>
       <c r="I115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J115">
         <v>1.01</v>
       </c>
       <c r="K115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O115" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q115" s="9"/>
+    </row>
+    <row r="116" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -6500,43 +6752,45 @@
         <v>187</v>
       </c>
       <c r="D116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K116" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L116">
         <v>0.217</v>
       </c>
       <c r="M116" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N116" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O116">
         <v>0.217</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q116" s="9"/>
+      <c r="R116" s="9"/>
+    </row>
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -6547,25 +6801,25 @@
         <v>187</v>
       </c>
       <c r="D117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K117">
         <v>2.2949999999999999</v>
@@ -6574,16 +6828,18 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="M117" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N117" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O117">
         <v>2.9079999999999999</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+    </row>
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -6594,43 +6850,45 @@
         <v>187</v>
       </c>
       <c r="D118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J118" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K118" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L118">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="M118" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N118" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O118" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+    </row>
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>132</v>
       </c>
@@ -6641,43 +6899,45 @@
         <v>187</v>
       </c>
       <c r="D119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J119" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K119" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L119" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M119" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N119" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O119" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+    </row>
+    <row r="120" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>133</v>
       </c>
@@ -6688,25 +6948,25 @@
         <v>187</v>
       </c>
       <c r="D120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K120">
         <v>1.302</v>
@@ -6715,14 +6975,15 @@
         <v>0.254</v>
       </c>
       <c r="M120" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N120" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O120">
         <v>1.556</v>
       </c>
+      <c r="Q120" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/cyano_atx_24.xlsx
+++ b/data/cyano_atx_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jld/Documents/Github/River_HAB_Modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1D7D62-0E10-CB43-A137-F59A8E84EEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2199ED-7C15-C945-B470-AED90827D9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/cyano_atx_24.xlsx
+++ b/data/cyano_atx_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jld/Documents/Github/River_HAB_Modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2199ED-7C15-C945-B470-AED90827D9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3631FF-D213-F44A-87C6-734065D07D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="27700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="219">
   <si>
     <t>ESF</t>
   </si>
@@ -790,7 +790,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2677,28 +2677,28 @@
     </row>
     <row r="33" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E33">
-        <v>0.47499999999999998</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="F33">
-        <v>0.159</v>
+        <v>0.17</v>
       </c>
       <c r="G33" t="s">
         <v>208</v>
       </c>
       <c r="H33">
-        <v>9.0999999999999998E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="I33" t="s">
         <v>208</v>
@@ -2707,10 +2707,10 @@
         <v>0.05</v>
       </c>
       <c r="K33">
-        <v>0.43</v>
+        <v>1.901</v>
       </c>
       <c r="L33">
-        <v>4.4999999999999998E-2</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="M33" t="s">
         <v>208</v>
@@ -2719,17 +2719,17 @@
         <v>208</v>
       </c>
       <c r="O33">
-        <v>0.47499999999999998</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
     </row>
     <row r="34" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>187</v>
@@ -2738,28 +2738,28 @@
         <v>218</v>
       </c>
       <c r="E34">
-        <v>0.47099999999999997</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F34">
-        <v>0.214</v>
+        <v>0.159</v>
       </c>
       <c r="G34" t="s">
         <v>208</v>
       </c>
       <c r="H34">
-        <v>0.122</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="I34" t="s">
         <v>208</v>
       </c>
       <c r="J34">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K34">
-        <v>0.41799999999999998</v>
+        <v>0.43</v>
       </c>
       <c r="L34">
-        <v>5.2999999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="M34" t="s">
         <v>208</v>
@@ -2768,17 +2768,17 @@
         <v>208</v>
       </c>
       <c r="O34">
-        <v>0.47099999999999997</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
     </row>
     <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>187</v>
@@ -2787,28 +2787,28 @@
         <v>218</v>
       </c>
       <c r="E35">
-        <v>0.66800000000000004</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="F35">
-        <v>0.17299999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="G35" t="s">
         <v>208</v>
       </c>
       <c r="H35">
-        <v>9.9000000000000005E-2</v>
+        <v>0.122</v>
       </c>
       <c r="I35" t="s">
         <v>208</v>
       </c>
       <c r="J35">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K35">
-        <v>0.497</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="L35">
-        <v>0.17100000000000001</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="M35" t="s">
         <v>208</v>
@@ -2817,35 +2817,35 @@
         <v>208</v>
       </c>
       <c r="O35">
-        <v>0.66800000000000004</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
     </row>
     <row r="36" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>187</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E36">
-        <v>2.4969999999999999</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="F36">
-        <v>0.17</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="G36" t="s">
         <v>208</v>
       </c>
       <c r="H36">
-        <v>9.7000000000000003E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="I36" t="s">
         <v>208</v>
@@ -2854,10 +2854,10 @@
         <v>0.05</v>
       </c>
       <c r="K36">
-        <v>1.901</v>
+        <v>0.497</v>
       </c>
       <c r="L36">
-        <v>0.59599999999999997</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="M36" t="s">
         <v>208</v>
@@ -2866,7 +2866,7 @@
         <v>208</v>
       </c>
       <c r="O36">
-        <v>2.4969999999999999</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
@@ -5903,8 +5903,8 @@
       <c r="N98" t="s">
         <v>208</v>
       </c>
-      <c r="O98" t="s">
-        <v>208</v>
+      <c r="O98">
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="Q98" s="9"/>
       <c r="R98" s="9"/>
